--- a/database/event/5463/event_5463_evp_summary.xlsx
+++ b/database/event/5463/event_5463_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.1625</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4198</v>
+        <v>2.358</v>
       </c>
       <c r="E2" t="n">
         <v>7.0329</v>
@@ -548,7 +548,7 @@
         <v>1.6107</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6948</v>
+        <v>1.6431</v>
       </c>
       <c r="E3" t="n">
         <v>5.2384</v>
@@ -594,7 +594,7 @@
         <v>1.5991</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6796</v>
+        <v>1.628</v>
       </c>
       <c r="E4" t="n">
         <v>5.2006</v>
@@ -640,7 +640,7 @@
         <v>1.5231</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5797</v>
+        <v>1.5295</v>
       </c>
       <c r="E5" t="n">
         <v>4.9534</v>
@@ -686,7 +686,7 @@
         <v>1.1997</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1548</v>
+        <v>1.1105</v>
       </c>
       <c r="E6" t="n">
         <v>3.9017</v>
@@ -732,7 +732,7 @@
         <v>1.1847</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1351</v>
+        <v>1.091</v>
       </c>
       <c r="E7" t="n">
         <v>3.8528</v>
@@ -778,7 +778,7 @@
         <v>1.1606</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1035</v>
+        <v>1.0599</v>
       </c>
       <c r="E8" t="n">
         <v>3.7746</v>
@@ -824,7 +824,7 @@
         <v>0.9055</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7683</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>2.9448</v>
@@ -870,7 +870,7 @@
         <v>0.8683999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7196</v>
+        <v>0.6813</v>
       </c>
       <c r="E10" t="n">
         <v>2.8242</v>
@@ -916,7 +916,7 @@
         <v>0.5984</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3649</v>
+        <v>0.3315</v>
       </c>
       <c r="E11" t="n">
         <v>1.9463</v>
@@ -962,7 +962,7 @@
         <v>0.59</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3538</v>
+        <v>0.3205</v>
       </c>
       <c r="E12" t="n">
         <v>1.9188</v>
@@ -1008,7 +1008,7 @@
         <v>0.5893</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3529</v>
+        <v>0.3197</v>
       </c>
       <c r="E13" t="n">
         <v>1.9166</v>
@@ -1054,7 +1054,7 @@
         <v>0.5324</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2781</v>
+        <v>0.2459</v>
       </c>
       <c r="E14" t="n">
         <v>1.7314</v>
@@ -1100,7 +1100,7 @@
         <v>0.524</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2671</v>
+        <v>0.235</v>
       </c>
       <c r="E15" t="n">
         <v>1.7042</v>
@@ -1146,7 +1146,7 @@
         <v>0.477</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2053</v>
+        <v>0.1741</v>
       </c>
       <c r="E16" t="n">
         <v>1.5513</v>
@@ -1192,7 +1192,7 @@
         <v>0.2985</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0291</v>
+        <v>-0.0571</v>
       </c>
       <c r="E17" t="n">
         <v>0.9709</v>
@@ -1238,7 +1238,7 @@
         <v>0.2315</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1172</v>
+        <v>-0.144</v>
       </c>
       <c r="E18" t="n">
         <v>0.7528</v>
@@ -1284,7 +1284,7 @@
         <v>0.1456</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.23</v>
+        <v>-0.2552</v>
       </c>
       <c r="E19" t="n">
         <v>0.4736</v>
@@ -1330,7 +1330,7 @@
         <v>0.1238</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2587</v>
+        <v>-0.2835</v>
       </c>
       <c r="E20" t="n">
         <v>0.4026</v>
@@ -1376,7 +1376,7 @@
         <v>0.1142</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2713</v>
+        <v>-0.2959</v>
       </c>
       <c r="E21" t="n">
         <v>0.3715</v>
@@ -1422,7 +1422,7 @@
         <v>0.0965</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2945</v>
+        <v>-0.3188</v>
       </c>
       <c r="E22" t="n">
         <v>0.314</v>
@@ -1468,7 +1468,7 @@
         <v>0.0925</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2998</v>
+        <v>-0.3241</v>
       </c>
       <c r="E23" t="n">
         <v>0.3008</v>
@@ -1514,7 +1514,7 @@
         <v>0.08110000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3148</v>
+        <v>-0.3388</v>
       </c>
       <c r="E24" t="n">
         <v>0.2639</v>
@@ -1560,7 +1560,7 @@
         <v>0.0427</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3652</v>
+        <v>-0.3886</v>
       </c>
       <c r="E25" t="n">
         <v>0.1389</v>
@@ -1606,7 +1606,7 @@
         <v>0.0154</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4011</v>
+        <v>-0.424</v>
       </c>
       <c r="E26" t="n">
         <v>0.0501</v>
@@ -1652,7 +1652,7 @@
         <v>0.0045</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4154</v>
+        <v>-0.4381</v>
       </c>
       <c r="E27" t="n">
         <v>0.0147</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0027</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4249</v>
+        <v>-0.4474</v>
       </c>
       <c r="E28" t="n">
         <v>-0.008800000000000001</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0181</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4452</v>
+        <v>-0.4674</v>
       </c>
       <c r="E29" t="n">
         <v>-0.059</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0907</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5405</v>
+        <v>-0.5614</v>
       </c>
       <c r="E30" t="n">
         <v>-0.295</v>
@@ -1836,7 +1836,7 @@
         <v>-0.09660000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5483</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3142</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1897</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6707</v>
+        <v>-0.6898</v>
       </c>
       <c r="E32" t="n">
         <v>-0.6171</v>
@@ -1928,7 +1928,7 @@
         <v>-0.2333</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7279</v>
+        <v>-0.7462</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7587</v>
@@ -1974,7 +1974,7 @@
         <v>-0.2543</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7554999999999999</v>
+        <v>-0.7734</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8270999999999999</v>
@@ -2020,7 +2020,7 @@
         <v>-0.3562</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8893</v>
+        <v>-0.9054</v>
       </c>
       <c r="E35" t="n">
         <v>-1.1584</v>
@@ -2066,7 +2066,7 @@
         <v>-0.3892</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9328</v>
+        <v>-0.9482</v>
       </c>
       <c r="E36" t="n">
         <v>-1.2659</v>
@@ -2112,7 +2112,7 @@
         <v>-0.3965</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9423</v>
+        <v>-0.9576</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2895</v>
@@ -2158,7 +2158,7 @@
         <v>-0.4044</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9527</v>
+        <v>-0.9679</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3153</v>
@@ -2204,7 +2204,7 @@
         <v>-0.509</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0901</v>
+        <v>-1.1035</v>
       </c>
       <c r="E39" t="n">
         <v>-1.6555</v>
@@ -2250,7 +2250,7 @@
         <v>-0.7631</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.424</v>
+        <v>-1.4327</v>
       </c>
       <c r="E40" t="n">
         <v>-2.4819</v>
@@ -2296,7 +2296,7 @@
         <v>-0.8310999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5132</v>
+        <v>-1.5207</v>
       </c>
       <c r="E41" t="n">
         <v>-2.7028</v>

--- a/database/event/5463/event_5463_evp_summary.xlsx
+++ b/database/event/5463/event_5463_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0329</v>
+        <v>6.685</v>
       </c>
       <c r="C2" t="n">
-        <v>2.1625</v>
+        <v>2.0555</v>
       </c>
       <c r="D2" t="n">
-        <v>2.358</v>
+        <v>2.3799</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0329</v>
+        <v>6.685</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4396</v>
+        <v>4.2432</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5933</v>
+        <v>2.4418</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3009</v>
+        <v>9.4641</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2965</v>
+        <v>4.9209</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5933</v>
+        <v>2.4418</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>146</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8898</v>
+        <v>7.3627</v>
       </c>
       <c r="N2" t="n">
         <v>299</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2384</v>
+        <v>5.121</v>
       </c>
       <c r="C3" t="n">
-        <v>1.6107</v>
+        <v>1.5746</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6431</v>
+        <v>1.6739</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2384</v>
+        <v>5.121</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2701</v>
+        <v>3.9547</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9683</v>
+        <v>1.1663</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6191</v>
+        <v>8.4475</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7439</v>
+        <v>4.3923</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9683</v>
+        <v>1.1663</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>146</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7122</v>
+        <v>5.558599999999999</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2006</v>
+        <v>4.8872</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5991</v>
+        <v>1.5027</v>
       </c>
       <c r="D4" t="n">
-        <v>1.628</v>
+        <v>1.5683</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2006</v>
+        <v>4.8872</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4217</v>
+        <v>4.0963</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7789</v>
+        <v>0.7909</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2291</v>
+        <v>8.9466</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2384</v>
+        <v>4.6518</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7789</v>
+        <v>0.7909</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>5.017300000000001</v>
+        <v>5.442699999999999</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9534</v>
+        <v>4.3848</v>
       </c>
       <c r="C5" t="n">
-        <v>1.5231</v>
+        <v>1.3482</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5295</v>
+        <v>1.3415</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9534</v>
+        <v>4.3848</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7781</v>
+        <v>3.2371</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1753</v>
+        <v>1.1477</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7781</v>
+        <v>5.9194</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0622</v>
+        <v>3.0778</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1753</v>
+        <v>1.1477</v>
       </c>
       <c r="K5" t="n">
         <v>114</v>
@@ -667,7 +667,7 @@
         <v>171</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2375</v>
+        <v>4.2255</v>
       </c>
       <c r="N5" t="n">
         <v>285</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9017</v>
+        <v>4.3486</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1997</v>
+        <v>1.3371</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1105</v>
+        <v>1.3252</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9017</v>
+        <v>4.3486</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6041</v>
+        <v>2.3374</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2976</v>
+        <v>2.0112</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6041</v>
+        <v>2.7491</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3002</v>
+        <v>1.4294</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2976</v>
+        <v>2.0112</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>146</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5978</v>
+        <v>3.4406</v>
       </c>
       <c r="N6" t="n">
         <v>299</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.8528</v>
+        <v>3.5509</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1847</v>
+        <v>1.0918</v>
       </c>
       <c r="D7" t="n">
-        <v>1.091</v>
+        <v>0.965</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8528</v>
+        <v>3.5509</v>
       </c>
       <c r="F7" t="n">
-        <v>3.7917</v>
+        <v>3.3015</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0611</v>
+        <v>0.2494</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7917</v>
+        <v>6.1461</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0733</v>
+        <v>3.1957</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0611</v>
+        <v>0.2494</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1344</v>
+        <v>3.4451</v>
       </c>
       <c r="N7" t="n">
         <v>285</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7746</v>
+        <v>3.5172</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1606</v>
+        <v>1.0815</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0599</v>
+        <v>0.9498</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7746</v>
+        <v>3.5172</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2306</v>
+        <v>2.9784</v>
       </c>
       <c r="G8" t="n">
-        <v>0.544</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2306</v>
+        <v>5.0077</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6185</v>
+        <v>2.6038</v>
       </c>
       <c r="J8" t="n">
-        <v>0.544</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>228</v>
@@ -805,7 +805,7 @@
         <v>81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1625</v>
+        <v>3.1426</v>
       </c>
       <c r="N8" t="n">
         <v>309</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9448</v>
+        <v>3.2092</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9055</v>
+        <v>0.9868</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.8108</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9448</v>
+        <v>3.2092</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9448</v>
+        <v>3.2092</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9448</v>
+        <v>3.6871</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9448</v>
+        <v>3.6871</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9448</v>
+        <v>3.6871</v>
       </c>
       <c r="N9" t="n">
         <v>189</v>
@@ -860,185 +860,185 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>apEX</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8242</v>
+        <v>2.9094</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8683999999999999</v>
+        <v>0.8946</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6813</v>
+        <v>0.6754</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8242</v>
+        <v>2.9094</v>
       </c>
       <c r="F10" t="n">
-        <v>3.0041</v>
+        <v>2.2836</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1799</v>
+        <v>0.6258</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0041</v>
+        <v>2.5598</v>
       </c>
       <c r="I10" t="n">
-        <v>2.4349</v>
+        <v>1.331</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1799</v>
+        <v>0.6258</v>
       </c>
       <c r="K10" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="M10" t="n">
-        <v>2.255</v>
+        <v>1.9568</v>
       </c>
       <c r="N10" t="n">
-        <v>214</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>apEX</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.9463</v>
+        <v>2.8255</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5984</v>
+        <v>0.8688</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3315</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9463</v>
+        <v>2.8255</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4888</v>
+        <v>2.9274</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4575</v>
+        <v>-0.1019</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4888</v>
+        <v>4.8281</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2067</v>
+        <v>2.5104</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4575</v>
+        <v>-0.1019</v>
       </c>
       <c r="K11" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="L11" t="n">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6642</v>
+        <v>2.4085</v>
       </c>
       <c r="N11" t="n">
-        <v>285</v>
+        <v>214</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9188</v>
+        <v>2.6153</v>
       </c>
       <c r="C12" t="n">
-        <v>0.59</v>
+        <v>0.8041</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3205</v>
+        <v>0.5427</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9188</v>
+        <v>2.6153</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9188</v>
+        <v>2.3856</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.2297</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9188</v>
+        <v>2.9189</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9188</v>
+        <v>1.5177</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.2297</v>
       </c>
       <c r="K12" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9188</v>
+        <v>1.7474</v>
       </c>
       <c r="N12" t="n">
-        <v>189</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9166</v>
+        <v>2.5063</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5893</v>
+        <v>0.7706</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3197</v>
+        <v>0.4935</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9166</v>
+        <v>2.5063</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3442</v>
+        <v>2.5063</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2608</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3442</v>
+        <v>2.5063</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.279</v>
+        <v>2.5063</v>
       </c>
       <c r="J13" t="n">
-        <v>2.2608</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="L13" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9818</v>
+        <v>2.5063</v>
       </c>
       <c r="N13" t="n">
-        <v>299</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7314</v>
+        <v>2.5022</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5324</v>
+        <v>0.7694</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2459</v>
+        <v>0.4916</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7314</v>
+        <v>2.5022</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2004</v>
+        <v>1.0963</v>
       </c>
       <c r="G14" t="n">
-        <v>1.531</v>
+        <v>1.4059</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2004</v>
+        <v>1.0963</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1624</v>
+        <v>0.57</v>
       </c>
       <c r="J14" t="n">
-        <v>1.531</v>
+        <v>1.4059</v>
       </c>
       <c r="K14" t="n">
         <v>153</v>
@@ -1081,7 +1081,7 @@
         <v>146</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6934</v>
+        <v>1.9759</v>
       </c>
       <c r="N14" t="n">
         <v>299</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7042</v>
+        <v>2.497</v>
       </c>
       <c r="C15" t="n">
-        <v>0.524</v>
+        <v>0.7678</v>
       </c>
       <c r="D15" t="n">
-        <v>0.235</v>
+        <v>0.4893</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7042</v>
+        <v>2.497</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5322</v>
+        <v>1.7375</v>
       </c>
       <c r="G15" t="n">
-        <v>0.172</v>
+        <v>0.7595</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5322</v>
+        <v>1.7375</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2419</v>
+        <v>0.9034</v>
       </c>
       <c r="J15" t="n">
-        <v>0.172</v>
+        <v>0.7595</v>
       </c>
       <c r="K15" t="n">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="L15" t="n">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4139</v>
+        <v>1.6629</v>
       </c>
       <c r="N15" t="n">
-        <v>309</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5513</v>
+        <v>1.9825</v>
       </c>
       <c r="C16" t="n">
-        <v>0.477</v>
+        <v>0.6096</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1741</v>
+        <v>0.257</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5513</v>
+        <v>1.9825</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9322</v>
+        <v>0.021</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6191</v>
+        <v>1.9615</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9322</v>
+        <v>0.021</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7556</v>
+        <v>0.0109</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6191</v>
+        <v>1.9615</v>
       </c>
       <c r="K16" t="n">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="L16" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3747</v>
+        <v>1.9724</v>
       </c>
       <c r="N16" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2985</v>
+        <v>0.4477</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0571</v>
+        <v>0.0193</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9709</v>
+        <v>1.4561</v>
       </c>
       <c r="N17" t="n">
         <v>198</v>
@@ -1228,170 +1228,170 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7528</v>
+        <v>0.9547</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2315</v>
+        <v>0.2936</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.144</v>
+        <v>-0.207</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7528</v>
+        <v>0.9547</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7528</v>
+        <v>1.3595</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-0.4048</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7528</v>
+        <v>1.3595</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7528</v>
+        <v>0.7069</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-0.4048</v>
       </c>
       <c r="K18" t="n">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7528</v>
+        <v>0.3021</v>
       </c>
       <c r="N18" t="n">
-        <v>198</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1456</v>
+        <v>0.273</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2552</v>
+        <v>-0.2372</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4736</v>
+        <v>0.8879</v>
       </c>
       <c r="N19" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1238</v>
+        <v>0.2434</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2835</v>
+        <v>-0.2807</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4026</v>
+        <v>0.7915</v>
       </c>
       <c r="N20" t="n">
-        <v>133</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1142</v>
+        <v>0.2032</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2959</v>
+        <v>-0.3397</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3715</v>
+        <v>0.6607</v>
       </c>
       <c r="N21" t="n">
         <v>129</v>
@@ -1412,492 +1412,492 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.314</v>
+        <v>0.6469</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0965</v>
+        <v>0.1989</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3188</v>
+        <v>-0.346</v>
       </c>
       <c r="E22" t="n">
-        <v>0.314</v>
+        <v>0.6469</v>
       </c>
       <c r="F22" t="n">
-        <v>0.314</v>
+        <v>1.1214</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.4745</v>
       </c>
       <c r="H22" t="n">
-        <v>0.314</v>
+        <v>1.1214</v>
       </c>
       <c r="I22" t="n">
-        <v>0.314</v>
+        <v>0.5831</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.4745</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M22" t="n">
-        <v>0.314</v>
+        <v>0.1086</v>
       </c>
       <c r="N22" t="n">
-        <v>129</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0925</v>
+        <v>0.1819</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3241</v>
+        <v>-0.371</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3008</v>
+        <v>0.5915</v>
       </c>
       <c r="N23" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="C24" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.1636</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3388</v>
+        <v>-0.3978</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>198</v>
+        <v>133</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2639</v>
+        <v>0.5321</v>
       </c>
       <c r="N24" t="n">
-        <v>198</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0427</v>
+        <v>0.1575</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3886</v>
+        <v>-0.4068</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1389</v>
+        <v>0.5121</v>
       </c>
       <c r="N25" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0501</v>
+        <v>0.5084</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0154</v>
+        <v>0.1563</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.424</v>
+        <v>-0.4085</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0501</v>
+        <v>0.5084</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0501</v>
+        <v>0.591</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0501</v>
+        <v>0.591</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0501</v>
+        <v>0.3073</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0501</v>
+        <v>0.2247</v>
       </c>
       <c r="N26" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0147</v>
+        <v>0.4629</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0045</v>
+        <v>0.1423</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4381</v>
+        <v>-0.429</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0147</v>
+        <v>0.4629</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6768</v>
+        <v>0.4629</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6768</v>
+        <v>0.4629</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5486</v>
+        <v>0.4629</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.6621</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="L27" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1135</v>
+        <v>0.4629</v>
       </c>
       <c r="N27" t="n">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.4315</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0027</v>
+        <v>0.1327</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4474</v>
+        <v>-0.4432</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.4315</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1083</v>
+        <v>0.4315</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1171</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1083</v>
+        <v>0.4315</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0878</v>
+        <v>0.4315</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1171</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="L28" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02929999999999999</v>
+        <v>0.4315</v>
       </c>
       <c r="N28" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.059</v>
+        <v>0.4179</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0181</v>
+        <v>0.1285</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4674</v>
+        <v>-0.4494</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.059</v>
+        <v>0.4179</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.059</v>
+        <v>1.0755</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.6576</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.059</v>
+        <v>1.0755</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.059</v>
+        <v>0.5592</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.6576</v>
       </c>
       <c r="K29" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.059</v>
+        <v>-0.09839999999999993</v>
       </c>
       <c r="N29" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.295</v>
+        <v>0.4137</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0907</v>
+        <v>0.1272</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5614</v>
+        <v>-0.4512</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.295</v>
+        <v>0.4137</v>
       </c>
       <c r="F30" t="n">
-        <v>0.524</v>
+        <v>0.4137</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.819</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.524</v>
+        <v>0.4137</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4247</v>
+        <v>0.4137</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.819</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="L30" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3942999999999999</v>
+        <v>0.4137</v>
       </c>
       <c r="N30" t="n">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.5646</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3142</v>
+        <v>0.1627</v>
       </c>
       <c r="N31" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1897</v>
+        <v>-0.0376</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6898</v>
+        <v>-0.6932</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6171</v>
+        <v>-0.1222</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.2333</v>
+        <v>-0.0973</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7462</v>
+        <v>-0.7809</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7587</v>
+        <v>-0.3165</v>
       </c>
       <c r="N33" t="n">
         <v>198</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.3527</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2543</v>
+        <v>-0.1084</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7734</v>
+        <v>-0.7972</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.3527</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1729</v>
+        <v>-0.3527</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1729</v>
+        <v>-0.3527</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1401</v>
+        <v>-0.3527</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L34" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.8599</v>
+        <v>-0.3527</v>
       </c>
       <c r="N34" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3562</v>
+        <v>-0.1568</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9054</v>
+        <v>-0.8683</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1584</v>
+        <v>-0.51</v>
       </c>
       <c r="N35" t="n">
         <v>189</v>
@@ -2056,231 +2056,231 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3892</v>
+        <v>-0.2678</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9482</v>
+        <v>-1.0313</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.2659</v>
+        <v>-0.8711</v>
       </c>
       <c r="N36" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2895</v>
+        <v>-0.9183</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3965</v>
+        <v>-0.2824</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9576</v>
+        <v>-1.0526</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2895</v>
+        <v>-0.9183</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8697</v>
+        <v>-0.9183</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.4198</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8697</v>
+        <v>-0.9183</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7049</v>
+        <v>-0.9183</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.4198</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L37" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1247</v>
+        <v>-0.9183</v>
       </c>
       <c r="N37" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3153</v>
+        <v>-1.1703</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.4044</v>
+        <v>-0.3598</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9679</v>
+        <v>-1.1663</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3153</v>
+        <v>-1.1703</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7708</v>
+        <v>-0.9051</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4555</v>
+        <v>-0.2652</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7708</v>
+        <v>-0.9051</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4353</v>
+        <v>-0.4706</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4555</v>
+        <v>-0.2652</v>
       </c>
       <c r="K38" t="n">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="L38" t="n">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9798</v>
+        <v>-0.7358</v>
       </c>
       <c r="N38" t="n">
-        <v>285</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.509</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1035</v>
+        <v>-1.4365</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6555</v>
+        <v>-1.7688</v>
       </c>
       <c r="N39" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.4819</v>
+        <v>-1.8575</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.7631</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4327</v>
+        <v>-1.4766</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.4819</v>
+        <v>-1.8575</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.4819</v>
+        <v>-2.4429</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.5854</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.4819</v>
+        <v>-2.4429</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.4819</v>
+        <v>-1.2702</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.5854</v>
       </c>
       <c r="K40" t="n">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.4819</v>
+        <v>-0.6848</v>
       </c>
       <c r="N40" t="n">
-        <v>189</v>
+        <v>285</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7028</v>
+        <v>-3.0836</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.9481000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5207</v>
+        <v>-2.0301</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7028</v>
+        <v>-3.0836</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.4204</v>
+        <v>-2.9376</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.2824</v>
+        <v>-0.146</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.4204</v>
+        <v>-2.9376</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.9618</v>
+        <v>-1.5274</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.2824</v>
+        <v>-0.146</v>
       </c>
       <c r="K41" t="n">
         <v>228</v>
@@ -2323,7 +2323,7 @@
         <v>81</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2442</v>
+        <v>-1.6734</v>
       </c>
       <c r="N41" t="n">
         <v>309</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2942</v>
+        <v>0.3263</v>
       </c>
       <c r="J2" t="n">
-        <v>12.3564</v>
+        <v>13.7046</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1561</v>
+        <v>0.1622</v>
       </c>
       <c r="J3" t="n">
-        <v>6.5562</v>
+        <v>6.8124</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0692</v>
+        <v>0.0664</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9064</v>
+        <v>2.7888</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2442</v>
+        <v>-0.145</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.2564</v>
+        <v>-6.09</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2607</v>
+        <v>-0.1559</v>
       </c>
       <c r="J6" t="n">
-        <v>-10.9494</v>
+        <v>-6.5478</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6443</v>
+        <v>0.6148</v>
       </c>
       <c r="J7" t="n">
-        <v>27.0606</v>
+        <v>25.8216</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.619</v>
+        <v>0.5896</v>
       </c>
       <c r="J8" t="n">
-        <v>25.998</v>
+        <v>24.7632</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4288</v>
+        <v>0.4078</v>
       </c>
       <c r="J9" t="n">
-        <v>18.0096</v>
+        <v>17.1276</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3365</v>
+        <v>0.3262</v>
       </c>
       <c r="J10" t="n">
-        <v>14.133</v>
+        <v>13.7004</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7917</v>
+        <v>-0.7467</v>
       </c>
       <c r="J11" t="n">
-        <v>-33.2514</v>
+        <v>-31.3614</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.089</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.6023</v>
+        <v>-1.869</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2092</v>
+        <v>-0.1798</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.3932</v>
+        <v>-3.7758</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.71</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3933</v>
+        <v>-0.2891</v>
       </c>
       <c r="J14" t="n">
-        <v>-8.2593</v>
+        <v>-6.0711</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4882</v>
+        <v>-0.3341</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.2522</v>
+        <v>-7.0161</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8016</v>
+        <v>-0.5488</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.8336</v>
+        <v>-11.5248</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.77</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6395</v>
+        <v>1.4241</v>
       </c>
       <c r="J17" t="n">
-        <v>34.4295</v>
+        <v>29.9061</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2263</v>
+        <v>1.1642</v>
       </c>
       <c r="J18" t="n">
-        <v>25.7523</v>
+        <v>24.4482</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5809</v>
+        <v>0.6874</v>
       </c>
       <c r="J19" t="n">
-        <v>12.1989</v>
+        <v>14.4354</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5345</v>
+        <v>0.6407</v>
       </c>
       <c r="J20" t="n">
-        <v>11.2245</v>
+        <v>13.4547</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3188</v>
+        <v>0.4189</v>
       </c>
       <c r="J21" t="n">
-        <v>6.6948</v>
+        <v>8.796900000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3502</v>
+        <v>0.3925</v>
       </c>
       <c r="J22" t="n">
-        <v>9.455399999999999</v>
+        <v>10.5975</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3044</v>
+        <v>0.3346</v>
       </c>
       <c r="J23" t="n">
-        <v>8.2188</v>
+        <v>9.0342</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1678</v>
+        <v>0.1687</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5306</v>
+        <v>4.5549</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.76</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4334</v>
+        <v>-0.275</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.7018</v>
+        <v>-7.425</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.488</v>
+        <v>-0.3137</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.176</v>
+        <v>-8.469900000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.39</v>
       </c>
       <c r="I27" t="n">
-        <v>1.051</v>
+        <v>1.0209</v>
       </c>
       <c r="J27" t="n">
-        <v>28.377</v>
+        <v>27.5643</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.449</v>
+        <v>0.4313</v>
       </c>
       <c r="J28" t="n">
-        <v>12.123</v>
+        <v>11.6451</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1408</v>
+        <v>0.1784</v>
       </c>
       <c r="J29" t="n">
-        <v>3.8016</v>
+        <v>4.8168</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0154</v>
+        <v>0.0338</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4158</v>
+        <v>0.9126</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.522</v>
+        <v>-0.4601</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.094</v>
+        <v>-12.4227</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3177</v>
+        <v>0.3372</v>
       </c>
       <c r="J32" t="n">
-        <v>8.260199999999999</v>
+        <v>8.767200000000001</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0911</v>
+        <v>0.0624</v>
       </c>
       <c r="J33" t="n">
-        <v>2.3686</v>
+        <v>1.6224</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1701</v>
+        <v>-0.1238</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.4226</v>
+        <v>-3.2188</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.217</v>
+        <v>-0.1445</v>
       </c>
       <c r="J35" t="n">
-        <v>-5.642</v>
+        <v>-3.757</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.54</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.702</v>
+        <v>-0.4722</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.252</v>
+        <v>-12.2772</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1347</v>
+        <v>0.8099</v>
       </c>
       <c r="J37" t="n">
-        <v>29.5022</v>
+        <v>21.0574</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0087</v>
+        <v>0.7309</v>
       </c>
       <c r="J38" t="n">
-        <v>26.2262</v>
+        <v>19.0034</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4611</v>
+        <v>0.4272</v>
       </c>
       <c r="J39" t="n">
-        <v>11.9886</v>
+        <v>11.1072</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3811</v>
+        <v>-0.3068</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.9086</v>
+        <v>-7.9768</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4107</v>
+        <v>-0.3373</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.6782</v>
+        <v>-8.7698</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4612</v>
+        <v>0.4537</v>
       </c>
       <c r="J42" t="n">
-        <v>13.836</v>
+        <v>13.611</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.053</v>
+        <v>0.0412</v>
       </c>
       <c r="J43" t="n">
-        <v>1.59</v>
+        <v>1.236</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2028</v>
+        <v>-0.1207</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.084</v>
+        <v>-3.621</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.271</v>
+        <v>-0.1643</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.130000000000001</v>
+        <v>-4.929</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3029</v>
+        <v>-0.1854</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.087</v>
+        <v>-5.562</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9603</v>
+        <v>0.694</v>
       </c>
       <c r="J47" t="n">
-        <v>28.809</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6574</v>
+        <v>0.5101</v>
       </c>
       <c r="J48" t="n">
-        <v>19.722</v>
+        <v>15.303</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2375</v>
+        <v>0.2675</v>
       </c>
       <c r="J49" t="n">
-        <v>7.125</v>
+        <v>8.025</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0229</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.391</v>
+        <v>-0.6870000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5775</v>
+        <v>-0.5172</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.325</v>
+        <v>-15.516</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.4363</v>
       </c>
       <c r="J52" t="n">
-        <v>15.3323</v>
+        <v>12.6527</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4445</v>
+        <v>0.3905</v>
       </c>
       <c r="J53" t="n">
-        <v>12.8905</v>
+        <v>11.3245</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3842</v>
+        <v>0.3593</v>
       </c>
       <c r="J54" t="n">
-        <v>11.1418</v>
+        <v>10.4197</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2053</v>
+        <v>0.2387</v>
       </c>
       <c r="J55" t="n">
-        <v>5.9537</v>
+        <v>6.9223</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1385</v>
+        <v>-0.0772</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.0165</v>
+        <v>-2.2388</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4517</v>
+        <v>0.4458</v>
       </c>
       <c r="J57" t="n">
-        <v>13.0993</v>
+        <v>12.9282</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.01</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0589</v>
+        <v>0.0435</v>
       </c>
       <c r="J58" t="n">
-        <v>1.7081</v>
+        <v>1.2615</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1797</v>
+        <v>-0.1081</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.2113</v>
+        <v>-3.1349</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2834</v>
+        <v>-0.1735</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.2186</v>
+        <v>-5.0315</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3753</v>
+        <v>-0.235</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.8837</v>
+        <v>-6.815</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2652</v>
+        <v>0.2116</v>
       </c>
       <c r="J62" t="n">
-        <v>7.1604</v>
+        <v>5.7132</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1347</v>
+        <v>0.0886</v>
       </c>
       <c r="J63" t="n">
-        <v>3.6369</v>
+        <v>2.3922</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1355</v>
+        <v>-0.1028</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.6585</v>
+        <v>-2.7756</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2764</v>
+        <v>-0.1765</v>
       </c>
       <c r="J65" t="n">
-        <v>-7.4628</v>
+        <v>-4.7655</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6173</v>
+        <v>-0.409</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.6671</v>
+        <v>-11.043</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3968</v>
+        <v>0.3387</v>
       </c>
       <c r="J67" t="n">
-        <v>10.7136</v>
+        <v>9.1449</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3679</v>
+        <v>0.3194</v>
       </c>
       <c r="J68" t="n">
-        <v>9.933299999999999</v>
+        <v>8.623799999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2703</v>
+        <v>0.2477</v>
       </c>
       <c r="J69" t="n">
-        <v>7.2981</v>
+        <v>6.6879</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1964</v>
+        <v>0.1969</v>
       </c>
       <c r="J70" t="n">
-        <v>5.3028</v>
+        <v>5.3163</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0965</v>
       </c>
       <c r="J71" t="n">
-        <v>2.0223</v>
+        <v>2.6055</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.9935</v>
       </c>
       <c r="J72" t="n">
-        <v>35</v>
+        <v>24.8375</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9507</v>
+        <v>0.7252</v>
       </c>
       <c r="J73" t="n">
-        <v>23.7675</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.31</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6935</v>
+        <v>0.6002</v>
       </c>
       <c r="J74" t="n">
-        <v>17.3375</v>
+        <v>15.005</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5032</v>
+        <v>0.4916</v>
       </c>
       <c r="J75" t="n">
-        <v>12.58</v>
+        <v>12.29</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.22</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4792</v>
+        <v>0.4775</v>
       </c>
       <c r="J76" t="n">
-        <v>11.98</v>
+        <v>11.9375</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1505</v>
+        <v>0.126</v>
       </c>
       <c r="J77" t="n">
-        <v>3.7625</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2756</v>
+        <v>-0.2264</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.89</v>
+        <v>-5.66</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.373</v>
+        <v>-0.2856</v>
       </c>
       <c r="J79" t="n">
-        <v>-9.324999999999999</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.732</v>
+        <v>-0.4979</v>
       </c>
       <c r="J80" t="n">
-        <v>-18.3</v>
+        <v>-12.4475</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.43</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.5448</v>
       </c>
       <c r="J81" t="n">
-        <v>-19.8975</v>
+        <v>-13.62</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2393</v>
+        <v>0.2372</v>
       </c>
       <c r="J82" t="n">
-        <v>5.9825</v>
+        <v>5.93</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1201</v>
+        <v>-0.1058</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.0025</v>
+        <v>-2.645</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1383</v>
+        <v>-0.1172</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.4575</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2944</v>
+        <v>-0.1995</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.36</v>
+        <v>-4.9875</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7651</v>
+        <v>-0.5203</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.1275</v>
+        <v>-13.0075</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8316</v>
+        <v>0.8359</v>
       </c>
       <c r="J87" t="n">
-        <v>20.79</v>
+        <v>20.8975</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7121</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>17.8025</v>
+        <v>18.0325</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7121</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>17.8025</v>
+        <v>18.0325</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2591</v>
+        <v>0.3277</v>
       </c>
       <c r="J90" t="n">
-        <v>6.4775</v>
+        <v>8.192500000000001</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.09</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2014</v>
+        <v>0.2711</v>
       </c>
       <c r="J91" t="n">
-        <v>5.035</v>
+        <v>6.7775</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3456</v>
+        <v>0.3769</v>
       </c>
       <c r="J92" t="n">
-        <v>9.331200000000001</v>
+        <v>10.1763</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>0.035</v>
+        <v>-0.0034</v>
       </c>
       <c r="J93" t="n">
-        <v>0.945</v>
+        <v>-0.09180000000000001</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.2538</v>
+        <v>-0.1722</v>
       </c>
       <c r="J94" t="n">
-        <v>-6.8526</v>
+        <v>-4.6494</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3874</v>
+        <v>-0.2514</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.4598</v>
+        <v>-6.7878</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.6843</v>
+        <v>-0.4592</v>
       </c>
       <c r="J96" t="n">
-        <v>-18.4761</v>
+        <v>-12.3984</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5065</v>
+        <v>1.3277</v>
       </c>
       <c r="J97" t="n">
-        <v>40.6755</v>
+        <v>35.8479</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.56</v>
       </c>
       <c r="I98" t="n">
-        <v>1.3355</v>
+        <v>1.2152</v>
       </c>
       <c r="J98" t="n">
-        <v>36.0585</v>
+        <v>32.8104</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0104</v>
+        <v>1.0026</v>
       </c>
       <c r="J99" t="n">
-        <v>27.2808</v>
+        <v>27.0702</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.73</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8919</v>
+        <v>-0.8536</v>
       </c>
       <c r="J100" t="n">
-        <v>-24.0813</v>
+        <v>-23.0472</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9357</v>
+        <v>-0.9025</v>
       </c>
       <c r="J101" t="n">
-        <v>-25.2639</v>
+        <v>-24.3675</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.48</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2071</v>
+        <v>1.1285</v>
       </c>
       <c r="J102" t="n">
-        <v>42.2485</v>
+        <v>39.4975</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5467</v>
+        <v>0.5448</v>
       </c>
       <c r="J103" t="n">
-        <v>19.1345</v>
+        <v>19.068</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.387</v>
+        <v>0.4208</v>
       </c>
       <c r="J104" t="n">
-        <v>13.545</v>
+        <v>14.728</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0366</v>
+        <v>0.097</v>
       </c>
       <c r="J105" t="n">
-        <v>1.281</v>
+        <v>3.395</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4321</v>
+        <v>-0.3614</v>
       </c>
       <c r="J106" t="n">
-        <v>-15.1235</v>
+        <v>-12.649</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7454</v>
+        <v>0.9264</v>
       </c>
       <c r="J107" t="n">
-        <v>26.089</v>
+        <v>32.424</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.3594</v>
+        <v>0.4061</v>
       </c>
       <c r="J108" t="n">
-        <v>12.579</v>
+        <v>14.2135</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2895</v>
+        <v>-0.1758</v>
       </c>
       <c r="J109" t="n">
-        <v>-10.1325</v>
+        <v>-6.153</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4913</v>
+        <v>-0.3156</v>
       </c>
       <c r="J110" t="n">
-        <v>-17.1955</v>
+        <v>-11.046</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.3441</v>
       </c>
       <c r="J111" t="n">
-        <v>-18.5745</v>
+        <v>-12.0435</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3269</v>
+        <v>1.2046</v>
       </c>
       <c r="J112" t="n">
-        <v>39.807</v>
+        <v>36.138</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1913</v>
+        <v>0.2133</v>
       </c>
       <c r="J113" t="n">
-        <v>5.739</v>
+        <v>6.399</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1547</v>
+        <v>0.1823</v>
       </c>
       <c r="J114" t="n">
-        <v>4.641</v>
+        <v>5.469</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1177</v>
+        <v>0.1499</v>
       </c>
       <c r="J115" t="n">
-        <v>3.531</v>
+        <v>4.497</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.9265</v>
+        <v>-0.8943</v>
       </c>
       <c r="J116" t="n">
-        <v>-27.795</v>
+        <v>-26.829</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.7728</v>
+        <v>0.9611</v>
       </c>
       <c r="J117" t="n">
-        <v>23.184</v>
+        <v>28.833</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0101</v>
+        <v>0.0325</v>
       </c>
       <c r="J118" t="n">
-        <v>0.303</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0608</v>
+        <v>-0.0242</v>
       </c>
       <c r="J119" t="n">
-        <v>-1.824</v>
+        <v>-0.726</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1092</v>
+        <v>-0.0541</v>
       </c>
       <c r="J120" t="n">
-        <v>-3.276</v>
+        <v>-1.623</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.3218</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.045</v>
+        <v>-9.654</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.84</v>
       </c>
       <c r="I122" t="n">
-        <v>1.8751</v>
+        <v>1.5835</v>
       </c>
       <c r="J122" t="n">
-        <v>52.5028</v>
+        <v>44.338</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2655</v>
+        <v>0.3143</v>
       </c>
       <c r="J123" t="n">
-        <v>7.434</v>
+        <v>8.8004</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0008</v>
+        <v>0.0605</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.0224</v>
+        <v>1.694</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2768</v>
+        <v>-0.2036</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.7504</v>
+        <v>-5.7008</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.82</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.668</v>
+        <v>-0.6101</v>
       </c>
       <c r="J126" t="n">
-        <v>-18.704</v>
+        <v>-17.0828</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3434</v>
+        <v>0.3771</v>
       </c>
       <c r="J127" t="n">
-        <v>9.6152</v>
+        <v>10.5588</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1331</v>
+        <v>0.1146</v>
       </c>
       <c r="J128" t="n">
-        <v>3.7268</v>
+        <v>3.2088</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1598</v>
+        <v>-0.1141</v>
       </c>
       <c r="J129" t="n">
-        <v>-4.4744</v>
+        <v>-3.1948</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.261</v>
+        <v>-0.1667</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.308</v>
+        <v>-4.6676</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6554</v>
+        <v>-0.4372</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.3512</v>
+        <v>-12.2416</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9371</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>25.3017</v>
+        <v>25.218</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.915</v>
+        <v>0.9123</v>
       </c>
       <c r="J133" t="n">
-        <v>24.705</v>
+        <v>24.6321</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4473</v>
+        <v>0.4905</v>
       </c>
       <c r="J134" t="n">
-        <v>12.0771</v>
+        <v>13.2435</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1541</v>
+        <v>0.2188</v>
       </c>
       <c r="J135" t="n">
-        <v>4.1607</v>
+        <v>5.9076</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2553</v>
+        <v>-0.178</v>
       </c>
       <c r="J136" t="n">
-        <v>-6.8931</v>
+        <v>-4.806</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1517</v>
+        <v>0.138</v>
       </c>
       <c r="J137" t="n">
-        <v>4.0959</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.98</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0129</v>
+        <v>-0.0277</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.3483</v>
+        <v>-0.7479</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1682</v>
+        <v>-0.1144</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.5414</v>
+        <v>-3.0888</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2285</v>
+        <v>-0.1464</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.1695</v>
+        <v>-3.9528</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.433</v>
+        <v>-0.2776</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.691</v>
+        <v>-7.4952</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5274</v>
+        <v>0.6231</v>
       </c>
       <c r="J142" t="n">
-        <v>12.6576</v>
+        <v>14.9544</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1252</v>
+        <v>0.0994</v>
       </c>
       <c r="J143" t="n">
-        <v>3.0048</v>
+        <v>2.3856</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.75</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4206</v>
+        <v>-0.2721</v>
       </c>
       <c r="J144" t="n">
-        <v>-10.0944</v>
+        <v>-6.5304</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.68</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5189</v>
+        <v>-0.3392</v>
       </c>
       <c r="J145" t="n">
-        <v>-12.4536</v>
+        <v>-8.1408</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5851</v>
+        <v>-0.3863</v>
       </c>
       <c r="J146" t="n">
-        <v>-14.0424</v>
+        <v>-9.2712</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.02</v>
       </c>
       <c r="I147" t="n">
-        <v>2.0276</v>
+        <v>1.7406</v>
       </c>
       <c r="J147" t="n">
-        <v>48.6624</v>
+        <v>41.7744</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5301</v>
+        <v>0.6136</v>
       </c>
       <c r="J148" t="n">
-        <v>12.7224</v>
+        <v>14.7264</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3538</v>
+        <v>0.4405</v>
       </c>
       <c r="J149" t="n">
-        <v>8.491199999999999</v>
+        <v>10.572</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2754</v>
+        <v>0.3615</v>
       </c>
       <c r="J150" t="n">
-        <v>6.6096</v>
+        <v>8.676</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2921</v>
+        <v>-0.2066</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.0104</v>
+        <v>-4.9584</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5226</v>
+        <v>0.6226</v>
       </c>
       <c r="J152" t="n">
-        <v>18.291</v>
+        <v>21.791</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.4965</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>17.3775</v>
+        <v>20.587</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1056</v>
+        <v>-0.0531</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.696</v>
+        <v>-1.8585</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3472</v>
+        <v>-0.2123</v>
       </c>
       <c r="J155" t="n">
-        <v>-12.152</v>
+        <v>-7.4305</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4464</v>
+        <v>-0.2822</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.624</v>
+        <v>-9.877000000000001</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.49</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2427</v>
+        <v>1.1502</v>
       </c>
       <c r="J157" t="n">
-        <v>43.4945</v>
+        <v>40.257</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6452</v>
+        <v>0.6266</v>
       </c>
       <c r="J158" t="n">
-        <v>22.582</v>
+        <v>21.931</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0897</v>
+        <v>-0.0281</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.1395</v>
+        <v>-0.9835</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2654</v>
+        <v>-0.1962</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.289</v>
+        <v>-6.867</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3621</v>
+        <v>-0.2931</v>
       </c>
       <c r="J161" t="n">
-        <v>-12.6735</v>
+        <v>-10.2585</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.967</v>
+        <v>0.9434</v>
       </c>
       <c r="J162" t="n">
-        <v>29.01</v>
+        <v>28.302</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.265</v>
+        <v>0.2471</v>
       </c>
       <c r="J163" t="n">
-        <v>7.95</v>
+        <v>7.413</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.05</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1887</v>
+        <v>0.1865</v>
       </c>
       <c r="J164" t="n">
-        <v>5.661</v>
+        <v>5.595</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0487</v>
+        <v>-0.0098</v>
       </c>
       <c r="J165" t="n">
-        <v>-1.461</v>
+        <v>-0.294</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.78</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7342</v>
+        <v>-0.6869</v>
       </c>
       <c r="J166" t="n">
-        <v>-22.026</v>
+        <v>-20.607</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.2966</v>
+        <v>0.3359</v>
       </c>
       <c r="J167" t="n">
-        <v>8.898</v>
+        <v>10.077</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.2966</v>
+        <v>0.3359</v>
       </c>
       <c r="J168" t="n">
-        <v>8.898</v>
+        <v>10.077</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2484</v>
+        <v>0.2782</v>
       </c>
       <c r="J169" t="n">
-        <v>7.452</v>
+        <v>8.346</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1783</v>
+        <v>0.1978</v>
       </c>
       <c r="J170" t="n">
-        <v>5.349</v>
+        <v>5.934</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5644</v>
+        <v>-0.3681</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.932</v>
+        <v>-11.043</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>0.755</v>
+        <v>0.72</v>
       </c>
       <c r="J172" t="n">
-        <v>22.65</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="J173" t="n">
-        <v>2.886</v>
+        <v>2.142</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.132</v>
+        <v>-0.0751</v>
       </c>
       <c r="J174" t="n">
-        <v>-3.96</v>
+        <v>-2.253</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2752</v>
+        <v>-0.1659</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.256</v>
+        <v>-4.977</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.62</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6202</v>
+        <v>-0.41</v>
       </c>
       <c r="J176" t="n">
-        <v>-18.606</v>
+        <v>-12.3</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5735</v>
+        <v>0.5072</v>
       </c>
       <c r="J177" t="n">
-        <v>17.205</v>
+        <v>15.216</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4972</v>
+        <v>0.4401</v>
       </c>
       <c r="J178" t="n">
-        <v>14.916</v>
+        <v>13.203</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4571</v>
+        <v>0.4061</v>
       </c>
       <c r="J179" t="n">
-        <v>13.713</v>
+        <v>12.183</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.0761</v>
+        <v>0.1039</v>
       </c>
       <c r="J180" t="n">
-        <v>2.283</v>
+        <v>3.117</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.05</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0402</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="J181" t="n">
-        <v>1.206</v>
+        <v>2.172</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8193</v>
+        <v>0.8081</v>
       </c>
       <c r="J182" t="n">
-        <v>22.1211</v>
+        <v>21.8187</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5989</v>
+        <v>0.5933</v>
       </c>
       <c r="J183" t="n">
-        <v>16.1703</v>
+        <v>16.0191</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3538</v>
+        <v>0.3946</v>
       </c>
       <c r="J184" t="n">
-        <v>9.5526</v>
+        <v>10.6542</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2325</v>
+        <v>0.2852</v>
       </c>
       <c r="J185" t="n">
-        <v>6.2775</v>
+        <v>7.7004</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0356</v>
+        <v>0.0965</v>
       </c>
       <c r="J186" t="n">
-        <v>0.9612000000000001</v>
+        <v>2.6055</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I187" t="n">
-        <v>0.507</v>
+        <v>0.5972</v>
       </c>
       <c r="J187" t="n">
-        <v>13.689</v>
+        <v>16.1244</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0379</v>
+        <v>-0.0334</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.0233</v>
+        <v>-0.9018</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1586</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.2822</v>
+        <v>-2.5974</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2321</v>
+        <v>-0.141</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.2667</v>
+        <v>-3.807</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.73</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4728</v>
+        <v>-0.3032</v>
       </c>
       <c r="J191" t="n">
-        <v>-12.7656</v>
+        <v>-8.186400000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.8547</v>
       </c>
       <c r="J192" t="n">
-        <v>20.039</v>
+        <v>24.7863</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.1646</v>
+        <v>0.226</v>
       </c>
       <c r="J193" t="n">
-        <v>4.7734</v>
+        <v>6.554</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0506</v>
+        <v>0.0982</v>
       </c>
       <c r="J194" t="n">
-        <v>1.4674</v>
+        <v>2.8478</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0297</v>
+        <v>0.0738</v>
       </c>
       <c r="J195" t="n">
-        <v>0.8613</v>
+        <v>2.1402</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.96</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.1526</v>
+        <v>-0.0755</v>
       </c>
       <c r="J196" t="n">
-        <v>-4.4254</v>
+        <v>-2.1895</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4871</v>
+        <v>0.4265</v>
       </c>
       <c r="J197" t="n">
-        <v>14.1259</v>
+        <v>12.3685</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1154</v>
+        <v>0.0665</v>
       </c>
       <c r="J198" t="n">
-        <v>3.3466</v>
+        <v>1.9285</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1837</v>
+        <v>-0.1863</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.3273</v>
+        <v>-5.4027</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.333</v>
+        <v>-0.306</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.657</v>
+        <v>-8.874000000000001</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7458</v>
+        <v>-0.7084</v>
       </c>
       <c r="J201" t="n">
-        <v>-21.6282</v>
+        <v>-20.5436</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.5306</v>
+        <v>0.6314</v>
       </c>
       <c r="J202" t="n">
-        <v>18.571</v>
+        <v>22.099</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.15</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3061</v>
+        <v>0.3427</v>
       </c>
       <c r="J203" t="n">
-        <v>10.7135</v>
+        <v>11.9945</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2304</v>
+        <v>-0.1351</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.064</v>
+        <v>-4.7285</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2956</v>
+        <v>-0.1784</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.346</v>
+        <v>-6.244</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3563</v>
+        <v>-0.2198</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.4705</v>
+        <v>-7.693</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7379</v>
+        <v>0.711</v>
       </c>
       <c r="J207" t="n">
-        <v>25.8265</v>
+        <v>24.885</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4228</v>
+        <v>0.4058</v>
       </c>
       <c r="J208" t="n">
-        <v>14.798</v>
+        <v>14.203</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1436</v>
+        <v>0.1793</v>
       </c>
       <c r="J209" t="n">
-        <v>5.026</v>
+        <v>6.2755</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1436</v>
+        <v>0.1793</v>
       </c>
       <c r="J210" t="n">
-        <v>5.026</v>
+        <v>6.2755</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.251</v>
+        <v>-0.1876</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.785</v>
+        <v>-6.566</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1758</v>
+        <v>0.1589</v>
       </c>
       <c r="J212" t="n">
-        <v>4.7466</v>
+        <v>4.2903</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.4381</v>
+        <v>-2.2896</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0848</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.4381</v>
+        <v>-2.2896</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4439</v>
+        <v>-0.2891</v>
       </c>
       <c r="J215" t="n">
-        <v>-11.9853</v>
+        <v>-7.8057</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.581</v>
+        <v>-0.3839</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.687</v>
+        <v>-10.3653</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.65</v>
       </c>
       <c r="I217" t="n">
-        <v>1.497</v>
+        <v>1.322</v>
       </c>
       <c r="J217" t="n">
-        <v>40.419</v>
+        <v>35.694</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.2075</v>
+        <v>1.1344</v>
       </c>
       <c r="J218" t="n">
-        <v>32.6025</v>
+        <v>30.6288</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4147</v>
+        <v>0.4818</v>
       </c>
       <c r="J219" t="n">
-        <v>11.1969</v>
+        <v>13.0086</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3054</v>
+        <v>-0.2245</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.245799999999999</v>
+        <v>-6.0615</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5647</v>
+        <v>-0.4957</v>
       </c>
       <c r="J221" t="n">
-        <v>-15.2469</v>
+        <v>-13.3839</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.73</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2725</v>
+        <v>-0.2349</v>
       </c>
       <c r="J222" t="n">
-        <v>-5.1775</v>
+        <v>-4.4631</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.64</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.4112</v>
+        <v>-0.3289</v>
       </c>
       <c r="J223" t="n">
-        <v>-7.8128</v>
+        <v>-6.2491</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.5105</v>
+        <v>-0.3861</v>
       </c>
       <c r="J224" t="n">
-        <v>-9.6995</v>
+        <v>-7.3359</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.48</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.6903</v>
+        <v>-0.4762</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.1157</v>
+        <v>-9.047800000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.38</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.8298</v>
+        <v>-0.572</v>
       </c>
       <c r="J226" t="n">
-        <v>-15.7662</v>
+        <v>-10.868</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.87</v>
       </c>
       <c r="I227" t="n">
-        <v>1.748</v>
+        <v>1.506</v>
       </c>
       <c r="J227" t="n">
-        <v>33.212</v>
+        <v>28.614</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.82</v>
       </c>
       <c r="I228" t="n">
-        <v>1.6605</v>
+        <v>1.4504</v>
       </c>
       <c r="J228" t="n">
-        <v>31.5495</v>
+        <v>27.5576</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I229" t="n">
-        <v>1.3646</v>
+        <v>1.2706</v>
       </c>
       <c r="J229" t="n">
-        <v>25.9274</v>
+        <v>24.1414</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.5</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0113</v>
+        <v>1.0889</v>
       </c>
       <c r="J230" t="n">
-        <v>19.2147</v>
+        <v>20.6891</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3122</v>
+        <v>-0.2227</v>
       </c>
       <c r="J231" t="n">
-        <v>-5.9318</v>
+        <v>-4.2313</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.9051</v>
+        <v>0.8899</v>
       </c>
       <c r="J232" t="n">
-        <v>30.7734</v>
+        <v>30.2566</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.25</v>
       </c>
       <c r="I233" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.6998</v>
       </c>
       <c r="J233" t="n">
-        <v>24.4562</v>
+        <v>23.7932</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.22</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6452</v>
+        <v>0.6266</v>
       </c>
       <c r="J234" t="n">
-        <v>21.9368</v>
+        <v>21.3044</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5676</v>
+        <v>0.5522</v>
       </c>
       <c r="J235" t="n">
-        <v>19.2984</v>
+        <v>18.7748</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.1293</v>
+        <v>-1.1213</v>
       </c>
       <c r="J236" t="n">
-        <v>-38.3962</v>
+        <v>-38.1242</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.1</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2402</v>
+        <v>0.2549</v>
       </c>
       <c r="J237" t="n">
-        <v>8.1668</v>
+        <v>8.666600000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.058</v>
+        <v>0.0431</v>
       </c>
       <c r="J238" t="n">
-        <v>1.972</v>
+        <v>1.4654</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.93</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1614</v>
+        <v>-0.0968</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.4876</v>
+        <v>-3.2912</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.3746</v>
+        <v>-4.4438</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2169</v>
+        <v>-0.1307</v>
       </c>
       <c r="J241" t="n">
-        <v>-7.3746</v>
+        <v>-4.4438</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4192</v>
+        <v>1.2693</v>
       </c>
       <c r="J242" t="n">
-        <v>35.48</v>
+        <v>31.7325</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>1.1019</v>
+        <v>1.0649</v>
       </c>
       <c r="J243" t="n">
-        <v>27.5475</v>
+        <v>26.6225</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3241</v>
+        <v>0.3856</v>
       </c>
       <c r="J244" t="n">
-        <v>8.102499999999999</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.02</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.0212</v>
+        <v>0.0484</v>
       </c>
       <c r="J245" t="n">
-        <v>-0.53</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.79</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.6999</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.8125</v>
+        <v>-17.4975</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.13</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3041</v>
+        <v>0.3289</v>
       </c>
       <c r="J247" t="n">
-        <v>7.6025</v>
+        <v>8.2225</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.01</v>
       </c>
       <c r="I248" t="n">
-        <v>0.076</v>
+        <v>0.0523</v>
       </c>
       <c r="J248" t="n">
-        <v>1.9</v>
+        <v>1.3075</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.076</v>
+        <v>0.0523</v>
       </c>
       <c r="J249" t="n">
-        <v>1.9</v>
+        <v>1.3075</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.75</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4372</v>
+        <v>-0.2796</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.93</v>
+        <v>-6.99</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4512</v>
+        <v>-0.2893</v>
       </c>
       <c r="J251" t="n">
-        <v>-11.28</v>
+        <v>-7.2325</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7937</v>
+        <v>0.7834</v>
       </c>
       <c r="J252" t="n">
-        <v>22.2236</v>
+        <v>21.9352</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.27</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7464</v>
+        <v>0.7363</v>
       </c>
       <c r="J253" t="n">
-        <v>20.8992</v>
+        <v>20.6164</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6479</v>
+        <v>0.6408</v>
       </c>
       <c r="J254" t="n">
-        <v>18.1412</v>
+        <v>17.9424</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.1994</v>
+        <v>0.2553</v>
       </c>
       <c r="J255" t="n">
-        <v>5.5832</v>
+        <v>7.1484</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4342</v>
+        <v>-0.363</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.1576</v>
+        <v>-10.164</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.07</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2225</v>
+        <v>0.22</v>
       </c>
       <c r="J257" t="n">
-        <v>6.23</v>
+        <v>6.16</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1607</v>
+        <v>-0.1225</v>
       </c>
       <c r="J258" t="n">
-        <v>-4.4996</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.87</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.227</v>
+        <v>-0.1536</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.356</v>
+        <v>-4.3008</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2994</v>
+        <v>-0.1942</v>
       </c>
       <c r="J260" t="n">
-        <v>-8.3832</v>
+        <v>-5.4376</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.72</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4659</v>
+        <v>-0.3022</v>
       </c>
       <c r="J261" t="n">
-        <v>-13.0452</v>
+        <v>-8.461600000000001</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.4406</v>
+        <v>0.3917</v>
       </c>
       <c r="J262" t="n">
-        <v>15.8616</v>
+        <v>14.1012</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.15</v>
       </c>
       <c r="I263" t="n">
-        <v>0.3098</v>
+        <v>0.2644</v>
       </c>
       <c r="J263" t="n">
-        <v>11.1528</v>
+        <v>9.5184</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.04</v>
       </c>
       <c r="I264" t="n">
-        <v>0.1154</v>
+        <v>0.0891</v>
       </c>
       <c r="J264" t="n">
-        <v>4.1544</v>
+        <v>3.2076</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0391</v>
+        <v>-0.0204</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.4076</v>
+        <v>-0.7344000000000001</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.6816</v>
+        <v>-0.4563</v>
       </c>
       <c r="J266" t="n">
-        <v>-24.5376</v>
+        <v>-16.4268</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.36</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5626</v>
+        <v>0.4857</v>
       </c>
       <c r="J267" t="n">
-        <v>20.2536</v>
+        <v>17.4852</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.32</v>
       </c>
       <c r="I268" t="n">
-        <v>0.5117</v>
+        <v>0.4386</v>
       </c>
       <c r="J268" t="n">
-        <v>18.4212</v>
+        <v>15.7896</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.2346</v>
+        <v>0.202</v>
       </c>
       <c r="J269" t="n">
-        <v>8.445600000000001</v>
+        <v>7.272</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2874</v>
+        <v>-0.1678</v>
       </c>
       <c r="J270" t="n">
-        <v>-10.3464</v>
+        <v>-6.0408</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.84</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3478</v>
+        <v>-0.2101</v>
       </c>
       <c r="J271" t="n">
-        <v>-12.5208</v>
+        <v>-7.5636</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9448</v>
+        <v>0.9258</v>
       </c>
       <c r="J272" t="n">
-        <v>33.068</v>
+        <v>32.403</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8777</v>
+        <v>0.8558</v>
       </c>
       <c r="J273" t="n">
-        <v>30.7195</v>
+        <v>29.953</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.0131</v>
+        <v>0.0349</v>
       </c>
       <c r="J274" t="n">
-        <v>-0.4585</v>
+        <v>1.2215</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.285</v>
+        <v>-0.221</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.975</v>
+        <v>-7.735</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.6246</v>
+        <v>-0.5677</v>
       </c>
       <c r="J276" t="n">
-        <v>-21.861</v>
+        <v>-19.8695</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.2</v>
       </c>
       <c r="I277" t="n">
-        <v>0.3767</v>
+        <v>0.4325</v>
       </c>
       <c r="J277" t="n">
-        <v>13.1845</v>
+        <v>15.1375</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.13</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2701</v>
+        <v>0.301</v>
       </c>
       <c r="J278" t="n">
-        <v>9.4535</v>
+        <v>10.535</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0514</v>
+        <v>-0.0221</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.799</v>
+        <v>-0.7735</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.143</v>
+        <v>-0.0779</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.005</v>
+        <v>-2.7265</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3444</v>
+        <v>-0.2109</v>
       </c>
       <c r="J281" t="n">
-        <v>-12.054</v>
+        <v>-7.3815</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4034</v>
+        <v>0.4585</v>
       </c>
       <c r="J282" t="n">
-        <v>11.6986</v>
+        <v>13.2965</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.01</v>
       </c>
       <c r="I283" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="J283" t="n">
-        <v>2.001</v>
+        <v>1.4007</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.059</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.1866</v>
+        <v>-1.711</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.8</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3693</v>
+        <v>-0.2323</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.7097</v>
+        <v>-6.7367</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.4412</v>
+        <v>-0.2816</v>
       </c>
       <c r="J286" t="n">
-        <v>-12.7948</v>
+        <v>-8.166399999999999</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.64</v>
       </c>
       <c r="I287" t="n">
-        <v>1.5175</v>
+        <v>1.3338</v>
       </c>
       <c r="J287" t="n">
-        <v>44.0075</v>
+        <v>38.6802</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9553</v>
+        <v>0.9453</v>
       </c>
       <c r="J288" t="n">
-        <v>27.7037</v>
+        <v>27.4137</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.0017</v>
+        <v>0.06</v>
       </c>
       <c r="J289" t="n">
-        <v>-0.0493</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4321</v>
+        <v>-0.3614</v>
       </c>
       <c r="J290" t="n">
-        <v>-12.5309</v>
+        <v>-10.4806</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6686</v>
+        <v>-0.6106</v>
       </c>
       <c r="J291" t="n">
-        <v>-19.3894</v>
+        <v>-17.7074</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.17</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3202</v>
+        <v>0.3683</v>
       </c>
       <c r="J292" t="n">
-        <v>11.5272</v>
+        <v>13.2588</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2234</v>
+        <v>0.2544</v>
       </c>
       <c r="J293" t="n">
-        <v>8.042400000000001</v>
+        <v>9.1584</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1688</v>
+        <v>0.1943</v>
       </c>
       <c r="J294" t="n">
-        <v>6.0768</v>
+        <v>6.9948</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.03</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0547</v>
+        <v>0.0848</v>
       </c>
       <c r="J295" t="n">
-        <v>1.9692</v>
+        <v>3.0528</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.88</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2758</v>
+        <v>-0.1622</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.928800000000001</v>
+        <v>-5.8392</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8129</v>
       </c>
       <c r="J297" t="n">
-        <v>29.7756</v>
+        <v>29.2644</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6841</v>
+        <v>0.67</v>
       </c>
       <c r="J298" t="n">
-        <v>24.6276</v>
+        <v>24.12</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3671</v>
+        <v>0.3969</v>
       </c>
       <c r="J299" t="n">
-        <v>13.2156</v>
+        <v>14.2884</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.13</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3671</v>
+        <v>0.3969</v>
       </c>
       <c r="J300" t="n">
-        <v>13.2156</v>
+        <v>14.2884</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.484</v>
+        <v>-0.4163</v>
       </c>
       <c r="J301" t="n">
-        <v>-17.424</v>
+        <v>-14.9868</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5463/event_5463_evp_summary.xlsx
+++ b/database/event/5463/event_5463_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.685</v>
+        <v>6.6342</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0555</v>
+        <v>2.0399</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3799</v>
+        <v>2.3958</v>
       </c>
       <c r="E2" t="n">
-        <v>6.685</v>
+        <v>6.6342</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2432</v>
+        <v>4.1859</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4418</v>
+        <v>2.4483</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4641</v>
+        <v>8.9168</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9209</v>
+        <v>4.815</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4418</v>
+        <v>2.4483</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>146</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3627</v>
+        <v>7.263300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>299</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.121</v>
+        <v>5.0367</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5746</v>
+        <v>1.5487</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6739</v>
+        <v>1.6686</v>
       </c>
       <c r="E3" t="n">
-        <v>5.121</v>
+        <v>5.0367</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9547</v>
+        <v>3.8811</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1663</v>
+        <v>1.1556</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4475</v>
+        <v>7.9109</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3923</v>
+        <v>4.2718</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1663</v>
+        <v>1.1556</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>146</v>
       </c>
       <c r="M3" t="n">
-        <v>5.558599999999999</v>
+        <v>5.4274</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8872</v>
+        <v>4.8676</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5027</v>
+        <v>1.4967</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5683</v>
+        <v>1.5916</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8872</v>
+        <v>4.8676</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0963</v>
+        <v>4.0304</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7909</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>8.9466</v>
+        <v>8.403600000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6518</v>
+        <v>4.5379</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7909</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>5.442699999999999</v>
+        <v>5.3751</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3848</v>
+        <v>4.4246</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3482</v>
+        <v>1.3605</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3415</v>
+        <v>1.39</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3848</v>
+        <v>4.4246</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2371</v>
+        <v>3.1778</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1477</v>
+        <v>1.2468</v>
       </c>
       <c r="H5" t="n">
-        <v>5.9194</v>
+        <v>5.5906</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0778</v>
+        <v>3.0189</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1477</v>
+        <v>1.2468</v>
       </c>
       <c r="K5" t="n">
         <v>114</v>
@@ -667,7 +667,7 @@
         <v>171</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2255</v>
+        <v>4.2657</v>
       </c>
       <c r="N5" t="n">
         <v>285</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3486</v>
+        <v>4.4087</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3371</v>
+        <v>1.3556</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3252</v>
+        <v>1.3827</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3486</v>
+        <v>4.4087</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3374</v>
+        <v>2.2861</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0112</v>
+        <v>2.1226</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7491</v>
+        <v>2.6486</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4294</v>
+        <v>1.4302</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0112</v>
+        <v>2.1226</v>
       </c>
       <c r="K6" t="n">
         <v>153</v>
@@ -713,7 +713,7 @@
         <v>146</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4406</v>
+        <v>3.5528</v>
       </c>
       <c r="N6" t="n">
         <v>299</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5509</v>
+        <v>3.5011</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0918</v>
+        <v>1.0765</v>
       </c>
       <c r="D7" t="n">
-        <v>0.965</v>
+        <v>0.9696</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5509</v>
+        <v>3.5011</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3015</v>
+        <v>3.2128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2494</v>
+        <v>0.2883</v>
       </c>
       <c r="H7" t="n">
-        <v>6.1461</v>
+        <v>5.706</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1957</v>
+        <v>3.0812</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2494</v>
+        <v>0.2883</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4451</v>
+        <v>3.3695</v>
       </c>
       <c r="N7" t="n">
         <v>285</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5172</v>
+        <v>3.4819</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0815</v>
+        <v>1.0706</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9498</v>
+        <v>0.9608</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5172</v>
+        <v>3.4819</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9784</v>
+        <v>2.9032</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5787</v>
       </c>
       <c r="H8" t="n">
-        <v>5.0077</v>
+        <v>4.6845</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6038</v>
+        <v>2.5296</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5787</v>
       </c>
       <c r="K8" t="n">
         <v>228</v>
@@ -805,7 +805,7 @@
         <v>81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1426</v>
+        <v>3.1083</v>
       </c>
       <c r="N8" t="n">
         <v>309</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>mantuu</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.2092</v>
+        <v>2.9123</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9868</v>
+        <v>0.8955</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8108</v>
+        <v>0.7015</v>
       </c>
       <c r="E9" t="n">
-        <v>3.2092</v>
+        <v>2.9123</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2092</v>
+        <v>2.2035</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.7088</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6871</v>
+        <v>2.376</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6871</v>
+        <v>1.283</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7088</v>
       </c>
       <c r="K9" t="n">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6871</v>
+        <v>1.9918</v>
       </c>
       <c r="N9" t="n">
-        <v>189</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mantuu</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9094</v>
+        <v>2.8653</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8946</v>
+        <v>0.881</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6754</v>
+        <v>0.6801</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9094</v>
+        <v>2.8653</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2836</v>
+        <v>2.8653</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6258</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5598</v>
+        <v>3.5464</v>
       </c>
       <c r="I10" t="n">
-        <v>1.331</v>
+        <v>3.5464</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6258</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="L10" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9568</v>
+        <v>3.5464</v>
       </c>
       <c r="N10" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8255</v>
+        <v>2.7258</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8688</v>
+        <v>0.8381</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6166</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8255</v>
+        <v>2.7258</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9274</v>
+        <v>2.8428</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1019</v>
+        <v>-0.117</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8281</v>
+        <v>4.4853</v>
       </c>
       <c r="I11" t="n">
-        <v>2.5104</v>
+        <v>2.422</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1019</v>
+        <v>-0.117</v>
       </c>
       <c r="K11" t="n">
         <v>158</v>
@@ -943,7 +943,7 @@
         <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>2.4085</v>
+        <v>2.305</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6153</v>
+        <v>2.6327</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8041</v>
+        <v>0.8095</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5427</v>
+        <v>0.5743</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6153</v>
+        <v>2.6327</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3856</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2297</v>
+        <v>1.6403</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9189</v>
+        <v>0.9923999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5177</v>
+        <v>0.5359</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2297</v>
+        <v>1.6403</v>
       </c>
       <c r="K12" t="n">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="L12" t="n">
-        <v>81</v>
+        <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7474</v>
+        <v>2.1762</v>
       </c>
       <c r="N12" t="n">
-        <v>309</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5063</v>
+        <v>2.4885</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7706</v>
+        <v>0.7652</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4935</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5063</v>
+        <v>2.4885</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5063</v>
+        <v>2.2857</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5063</v>
+        <v>2.6471</v>
       </c>
       <c r="I13" t="n">
-        <v>2.5063</v>
+        <v>1.4294</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.2028</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>2.5063</v>
+        <v>1.6322</v>
       </c>
       <c r="N13" t="n">
-        <v>189</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>NBK-</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.5022</v>
+        <v>2.4117</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7694</v>
+        <v>0.7415</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4916</v>
+        <v>0.4737</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5022</v>
+        <v>2.4117</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0963</v>
+        <v>1.6302</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4059</v>
+        <v>0.7815</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0963</v>
+        <v>1.6302</v>
       </c>
       <c r="I14" t="n">
-        <v>0.57</v>
+        <v>0.8803</v>
       </c>
       <c r="J14" t="n">
-        <v>1.4059</v>
+        <v>0.7815</v>
       </c>
       <c r="K14" t="n">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="L14" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9759</v>
+        <v>1.6618</v>
       </c>
       <c r="N14" t="n">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NBK-</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.497</v>
+        <v>2.3076</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7678</v>
+        <v>0.7095</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4893</v>
+        <v>0.4263</v>
       </c>
       <c r="E15" t="n">
-        <v>2.497</v>
+        <v>2.3076</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7375</v>
+        <v>2.3076</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7595</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7375</v>
+        <v>2.3257</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9034</v>
+        <v>2.3257</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7595</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="L15" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6629</v>
+        <v>2.3257</v>
       </c>
       <c r="N15" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.9825</v>
+        <v>2.2535</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6096</v>
+        <v>0.6929</v>
       </c>
       <c r="D16" t="n">
-        <v>0.257</v>
+        <v>0.4016</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9825</v>
+        <v>2.2535</v>
       </c>
       <c r="F16" t="n">
-        <v>0.021</v>
+        <v>0.152</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9615</v>
+        <v>2.1015</v>
       </c>
       <c r="H16" t="n">
-        <v>0.021</v>
+        <v>0.152</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0109</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9615</v>
+        <v>2.1015</v>
       </c>
       <c r="K16" t="n">
         <v>153</v>
@@ -1173,7 +1173,7 @@
         <v>146</v>
       </c>
       <c r="M16" t="n">
-        <v>1.9724</v>
+        <v>2.1836</v>
       </c>
       <c r="N16" t="n">
         <v>299</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4477</v>
+        <v>0.4026</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0193</v>
+        <v>-0.0282</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4561</v>
+        <v>1.3092</v>
       </c>
       <c r="N17" t="n">
         <v>198</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9547</v>
+        <v>0.9213</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2936</v>
+        <v>0.2833</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.207</v>
+        <v>-0.2048</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9547</v>
+        <v>0.9213</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3595</v>
+        <v>1.3137</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4048</v>
+        <v>-0.3924</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3595</v>
+        <v>1.3137</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7069</v>
+        <v>0.7094</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4048</v>
+        <v>-0.3924</v>
       </c>
       <c r="K18" t="n">
         <v>228</v>
@@ -1265,7 +1265,7 @@
         <v>81</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3021</v>
+        <v>0.317</v>
       </c>
       <c r="N18" t="n">
         <v>309</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="C19" t="n">
-        <v>0.273</v>
+        <v>0.2719</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2372</v>
+        <v>-0.2217</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8879</v>
+        <v>0.8843</v>
       </c>
       <c r="N19" t="n">
         <v>198</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2434</v>
+        <v>0.2384</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2807</v>
+        <v>-0.2713</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7915</v>
+        <v>0.7753</v>
       </c>
       <c r="N20" t="n">
         <v>189</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2032</v>
+        <v>0.1879</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3397</v>
+        <v>-0.346</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6607</v>
+        <v>0.6111</v>
       </c>
       <c r="N21" t="n">
         <v>129</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6469</v>
+        <v>0.5926</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1989</v>
+        <v>0.1822</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.346</v>
+        <v>-0.3544</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6469</v>
+        <v>0.5926</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1214</v>
+        <v>0.5926</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4745</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1214</v>
+        <v>0.5926</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5831</v>
+        <v>0.5926</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4745</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="L22" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1086</v>
+        <v>0.5926</v>
       </c>
       <c r="N22" t="n">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5915</v>
+        <v>0.5806</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1819</v>
+        <v>0.1785</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.371</v>
+        <v>-0.3599</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5915</v>
+        <v>0.5806</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5915</v>
+        <v>1.063</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.4824</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5915</v>
+        <v>1.063</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5915</v>
+        <v>0.574</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.4824</v>
       </c>
       <c r="K23" t="n">
-        <v>129</v>
+        <v>228</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5915</v>
+        <v>0.09159999999999996</v>
       </c>
       <c r="N23" t="n">
-        <v>129</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1636</v>
+        <v>0.1552</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3978</v>
+        <v>-0.3944</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5321</v>
+        <v>0.5049</v>
       </c>
       <c r="N24" t="n">
         <v>133</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1575</v>
+        <v>0.1488</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4068</v>
+        <v>-0.4039</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5121</v>
+        <v>0.4839</v>
       </c>
       <c r="N25" t="n">
         <v>133</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5084</v>
+        <v>0.447</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1563</v>
+        <v>0.1374</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4085</v>
+        <v>-0.4207</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5084</v>
+        <v>0.447</v>
       </c>
       <c r="F26" t="n">
-        <v>0.591</v>
+        <v>0.5402</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>0.591</v>
+        <v>0.5402</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3073</v>
+        <v>0.2917</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="K26" t="n">
         <v>158</v>
@@ -1633,7 +1633,7 @@
         <v>56</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2247</v>
+        <v>0.1985</v>
       </c>
       <c r="N26" t="n">
         <v>214</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1423</v>
+        <v>0.1315</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.429</v>
+        <v>-0.4296</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4629</v>
+        <v>0.4276</v>
       </c>
       <c r="N27" t="n">
         <v>129</v>
@@ -1688,139 +1688,139 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>JACKZ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1327</v>
+        <v>0.1303</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4432</v>
+        <v>-0.4313</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>198</v>
+        <v>129</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4315</v>
+        <v>0.4238</v>
       </c>
       <c r="N28" t="n">
-        <v>198</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4179</v>
+        <v>0.3794</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1285</v>
+        <v>0.1167</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4494</v>
+        <v>-0.4515</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4179</v>
+        <v>0.3794</v>
       </c>
       <c r="F29" t="n">
-        <v>1.0755</v>
+        <v>0.3794</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6576</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0755</v>
+        <v>0.3794</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5592</v>
+        <v>0.3794</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6576</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>158</v>
+        <v>198</v>
       </c>
       <c r="L29" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.09839999999999993</v>
+        <v>0.3794</v>
       </c>
       <c r="N29" t="n">
-        <v>214</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>JACKZ</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4137</v>
+        <v>0.3092</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1272</v>
+        <v>0.0951</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4512</v>
+        <v>-0.4834</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4137</v>
+        <v>0.3092</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4137</v>
+        <v>0.9887</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.6795</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4137</v>
+        <v>0.9887</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4137</v>
+        <v>0.5339</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.6795</v>
       </c>
       <c r="K30" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M30" t="n">
-        <v>0.4137</v>
+        <v>-0.1456</v>
       </c>
       <c r="N30" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="C31" t="n">
-        <v>0.05</v>
+        <v>0.0456</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5646</v>
+        <v>-0.5566</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1627</v>
+        <v>0.1484</v>
       </c>
       <c r="N31" t="n">
         <v>129</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0376</v>
+        <v>-0.0431</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6932</v>
+        <v>-0.6881</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1222</v>
+        <v>-0.1403</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0973</v>
+        <v>-0.107</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7809</v>
+        <v>-0.7826</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3165</v>
+        <v>-0.348</v>
       </c>
       <c r="N33" t="n">
         <v>198</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1084</v>
+        <v>-0.1176</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7972</v>
+        <v>-0.7983</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3527</v>
+        <v>-0.3825</v>
       </c>
       <c r="N34" t="n">
         <v>133</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1568</v>
+        <v>-0.1651</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8683</v>
+        <v>-0.8686</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.51</v>
+        <v>-0.5369</v>
       </c>
       <c r="N35" t="n">
         <v>189</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2678</v>
+        <v>-0.2859</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0313</v>
+        <v>-1.0475</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8711</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="N36" t="n">
         <v>198</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2824</v>
+        <v>-0.2934</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0526</v>
+        <v>-1.0586</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9183</v>
+        <v>-0.9543</v>
       </c>
       <c r="N37" t="n">
         <v>133</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1703</v>
+        <v>-1.0357</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3598</v>
+        <v>-0.3185</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1663</v>
+        <v>-1.0957</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1703</v>
+        <v>-1.0357</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9051</v>
+        <v>-0.7417</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.2652</v>
+        <v>-0.294</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9051</v>
+        <v>-0.7417</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4706</v>
+        <v>-0.4005</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.2652</v>
+        <v>-0.294</v>
       </c>
       <c r="K38" t="n">
         <v>158</v>
@@ -2185,7 +2185,7 @@
         <v>56</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.7358</v>
+        <v>-0.6945</v>
       </c>
       <c r="N38" t="n">
         <v>214</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NaToSaphiX</t>
+          <t>Aleksib</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.7688</v>
+        <v>-1.3963</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4293</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.4365</v>
+        <v>-1.2598</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.7688</v>
+        <v>-1.3963</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.7688</v>
+        <v>-2.0504</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.6541</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.7688</v>
+        <v>-2.0504</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.7688</v>
+        <v>-1.1072</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.6541</v>
       </c>
       <c r="K39" t="n">
-        <v>189</v>
+        <v>114</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7688</v>
+        <v>-0.4530999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>189</v>
+        <v>285</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Aleksib</t>
+          <t>NaToSaphiX</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8575</v>
+        <v>-1.7764</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.5462</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4766</v>
+        <v>-1.4329</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8575</v>
+        <v>-1.7764</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.4429</v>
+        <v>-1.7764</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5854</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.4429</v>
+        <v>-1.7764</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2702</v>
+        <v>-1.7764</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5854</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="L40" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.6848</v>
+        <v>-1.7764</v>
       </c>
       <c r="N40" t="n">
-        <v>285</v>
+        <v>189</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0836</v>
+        <v>-2.7862</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9481000000000001</v>
+        <v>-0.8567</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0301</v>
+        <v>-1.8925</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0836</v>
+        <v>-2.7862</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9376</v>
+        <v>-2.6236</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.146</v>
+        <v>-0.1626</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9376</v>
+        <v>-2.6236</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5274</v>
+        <v>-1.4167</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.146</v>
+        <v>-0.1626</v>
       </c>
       <c r="K41" t="n">
         <v>228</v>
@@ -2323,7 +2323,7 @@
         <v>81</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6734</v>
+        <v>-1.5793</v>
       </c>
       <c r="N41" t="n">
         <v>309</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3263</v>
+        <v>0.3284</v>
       </c>
       <c r="J2" t="n">
-        <v>13.7046</v>
+        <v>13.7928</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1622</v>
+        <v>0.1704</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8124</v>
+        <v>7.1568</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0664</v>
+        <v>0.0736</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7888</v>
+        <v>3.0912</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.145</v>
+        <v>-0.1581</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.09</v>
+        <v>-6.6402</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1559</v>
+        <v>-0.1691</v>
       </c>
       <c r="J6" t="n">
-        <v>-6.5478</v>
+        <v>-7.1022</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6148</v>
+        <v>0.5879</v>
       </c>
       <c r="J7" t="n">
-        <v>25.8216</v>
+        <v>24.6918</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5896</v>
+        <v>0.5654</v>
       </c>
       <c r="J8" t="n">
-        <v>24.7632</v>
+        <v>23.7468</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4078</v>
+        <v>0.4015</v>
       </c>
       <c r="J9" t="n">
-        <v>17.1276</v>
+        <v>16.863</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3262</v>
+        <v>0.3264</v>
       </c>
       <c r="J10" t="n">
-        <v>13.7004</v>
+        <v>13.7088</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7467</v>
+        <v>-0.6942</v>
       </c>
       <c r="J11" t="n">
-        <v>-31.3614</v>
+        <v>-29.1564</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.089</v>
+        <v>-0.1119</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.869</v>
+        <v>-2.3499</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1798</v>
+        <v>-0.2023</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7758</v>
+        <v>-4.2483</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.71</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2891</v>
+        <v>-0.3092</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.0711</v>
+        <v>-6.4932</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3341</v>
+        <v>-0.353</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.0161</v>
+        <v>-7.413</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5488</v>
+        <v>-0.5555</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.5248</v>
+        <v>-11.6655</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.77</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4241</v>
+        <v>1.5457</v>
       </c>
       <c r="J17" t="n">
-        <v>29.9061</v>
+        <v>32.4597</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1642</v>
+        <v>1.1832</v>
       </c>
       <c r="J18" t="n">
-        <v>24.4482</v>
+        <v>24.8472</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6874</v>
+        <v>0.6667</v>
       </c>
       <c r="J19" t="n">
-        <v>14.4354</v>
+        <v>14.0007</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6407</v>
+        <v>0.6252</v>
       </c>
       <c r="J20" t="n">
-        <v>13.4547</v>
+        <v>13.1292</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4189</v>
+        <v>0.4265</v>
       </c>
       <c r="J21" t="n">
-        <v>8.796900000000001</v>
+        <v>8.9565</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3925</v>
+        <v>0.3888</v>
       </c>
       <c r="J22" t="n">
-        <v>10.5975</v>
+        <v>10.4976</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3346</v>
+        <v>0.3345</v>
       </c>
       <c r="J23" t="n">
-        <v>9.0342</v>
+        <v>9.031499999999999</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1687</v>
+        <v>0.1751</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5549</v>
+        <v>4.7277</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.76</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.275</v>
+        <v>-0.2886</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.425</v>
+        <v>-7.7922</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3137</v>
+        <v>-0.3264</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.469900000000001</v>
+        <v>-8.812799999999999</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.39</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0209</v>
+        <v>0.9618</v>
       </c>
       <c r="J27" t="n">
-        <v>27.5643</v>
+        <v>25.9686</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4313</v>
+        <v>0.4236</v>
       </c>
       <c r="J28" t="n">
-        <v>11.6451</v>
+        <v>11.4372</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1784</v>
+        <v>0.1875</v>
       </c>
       <c r="J29" t="n">
-        <v>4.8168</v>
+        <v>5.0625</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0338</v>
+        <v>0.0454</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9126</v>
+        <v>1.2258</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4601</v>
+        <v>-0.4378</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.4227</v>
+        <v>-11.8206</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3372</v>
+        <v>0.3362</v>
       </c>
       <c r="J32" t="n">
-        <v>8.767200000000001</v>
+        <v>8.741199999999999</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0624</v>
+        <v>0.0612</v>
       </c>
       <c r="J33" t="n">
-        <v>1.6224</v>
+        <v>1.5912</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1238</v>
+        <v>-0.139</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.2188</v>
+        <v>-3.614</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1445</v>
+        <v>-0.1604</v>
       </c>
       <c r="J35" t="n">
-        <v>-3.757</v>
+        <v>-4.1704</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.54</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4722</v>
+        <v>-0.48</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.2772</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8099</v>
+        <v>0.8934</v>
       </c>
       <c r="J37" t="n">
-        <v>21.0574</v>
+        <v>23.2284</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7309</v>
+        <v>0.8079</v>
       </c>
       <c r="J38" t="n">
-        <v>19.0034</v>
+        <v>21.0054</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4272</v>
+        <v>0.4711</v>
       </c>
       <c r="J39" t="n">
-        <v>11.1072</v>
+        <v>12.2486</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3068</v>
+        <v>-0.2921</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.9768</v>
+        <v>-7.5946</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3373</v>
+        <v>-0.3205</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.7698</v>
+        <v>-8.333</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4537</v>
+        <v>0.501</v>
       </c>
       <c r="J42" t="n">
-        <v>13.611</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0412</v>
+        <v>0.0458</v>
       </c>
       <c r="J43" t="n">
-        <v>1.236</v>
+        <v>1.374</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1207</v>
+        <v>-0.1336</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.621</v>
+        <v>-4.008</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1643</v>
+        <v>-0.1782</v>
       </c>
       <c r="J45" t="n">
-        <v>-4.929</v>
+        <v>-5.346</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1854</v>
+        <v>-0.1995</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.562</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.694</v>
+        <v>0.7642</v>
       </c>
       <c r="J47" t="n">
-        <v>20.82</v>
+        <v>22.926</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5101</v>
+        <v>0.5619</v>
       </c>
       <c r="J48" t="n">
-        <v>15.303</v>
+        <v>16.857</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2675</v>
+        <v>0.2723</v>
       </c>
       <c r="J49" t="n">
-        <v>8.025</v>
+        <v>8.169</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0229</v>
+        <v>-0.0157</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-0.471</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5172</v>
+        <v>-0.489</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.516</v>
+        <v>-14.67</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4363</v>
+        <v>0.4789</v>
       </c>
       <c r="J52" t="n">
-        <v>12.6527</v>
+        <v>13.8881</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3905</v>
+        <v>0.4215</v>
       </c>
       <c r="J53" t="n">
-        <v>11.3245</v>
+        <v>12.2235</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3593</v>
+        <v>0.3741</v>
       </c>
       <c r="J54" t="n">
-        <v>10.4197</v>
+        <v>10.8489</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2387</v>
+        <v>0.245</v>
       </c>
       <c r="J55" t="n">
-        <v>6.9223</v>
+        <v>7.105</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.0772</v>
+        <v>-0.075</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.2388</v>
+        <v>-2.175</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4458</v>
+        <v>0.4912</v>
       </c>
       <c r="J57" t="n">
-        <v>12.9282</v>
+        <v>14.2448</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.01</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0435</v>
+        <v>0.0475</v>
       </c>
       <c r="J58" t="n">
-        <v>1.2615</v>
+        <v>1.3775</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1081</v>
+        <v>-0.1209</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.1349</v>
+        <v>-3.5061</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1735</v>
+        <v>-0.1879</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.0315</v>
+        <v>-5.4491</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.235</v>
+        <v>-0.2493</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.815</v>
+        <v>-7.2297</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2116</v>
+        <v>0.215</v>
       </c>
       <c r="J62" t="n">
-        <v>5.7132</v>
+        <v>5.805</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0886</v>
+        <v>0.0919</v>
       </c>
       <c r="J63" t="n">
-        <v>2.3922</v>
+        <v>2.4813</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1028</v>
+        <v>-0.1169</v>
       </c>
       <c r="J64" t="n">
-        <v>-2.7756</v>
+        <v>-3.1563</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1765</v>
+        <v>-0.1926</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.7655</v>
+        <v>-5.2002</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.409</v>
+        <v>-0.4197</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.043</v>
+        <v>-11.3319</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3387</v>
+        <v>0.3598</v>
       </c>
       <c r="J67" t="n">
-        <v>9.1449</v>
+        <v>9.714600000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3194</v>
+        <v>0.3365</v>
       </c>
       <c r="J68" t="n">
-        <v>8.623799999999999</v>
+        <v>9.0855</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2477</v>
+        <v>0.2649</v>
       </c>
       <c r="J69" t="n">
-        <v>6.6879</v>
+        <v>7.1523</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1969</v>
+        <v>0.2142</v>
       </c>
       <c r="J70" t="n">
-        <v>5.3163</v>
+        <v>5.7834</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.0965</v>
+        <v>0.1125</v>
       </c>
       <c r="J71" t="n">
-        <v>2.6055</v>
+        <v>3.0375</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9935</v>
+        <v>1.0982</v>
       </c>
       <c r="J72" t="n">
-        <v>24.8375</v>
+        <v>27.455</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7252</v>
+        <v>0.8086</v>
       </c>
       <c r="J73" t="n">
-        <v>18.13</v>
+        <v>20.215</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.31</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6002</v>
+        <v>0.6705</v>
       </c>
       <c r="J74" t="n">
-        <v>15.005</v>
+        <v>16.7625</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.4916</v>
+        <v>0.5496</v>
       </c>
       <c r="J75" t="n">
-        <v>12.29</v>
+        <v>13.74</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.22</v>
       </c>
       <c r="I76" t="n">
-        <v>0.4775</v>
+        <v>0.5337</v>
       </c>
       <c r="J76" t="n">
-        <v>11.9375</v>
+        <v>13.3425</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.126</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>3.15</v>
+        <v>2.3075</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.2264</v>
+        <v>-0.249</v>
       </c>
       <c r="J78" t="n">
-        <v>-5.66</v>
+        <v>-6.225</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2856</v>
+        <v>-0.3066</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.14</v>
+        <v>-7.665</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4979</v>
+        <v>-0.5087</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.4475</v>
+        <v>-12.7175</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.43</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5448</v>
+        <v>-0.5524</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.62</v>
+        <v>-13.81</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2372</v>
+        <v>0.2308</v>
       </c>
       <c r="J82" t="n">
-        <v>5.93</v>
+        <v>5.77</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1058</v>
+        <v>-0.1222</v>
       </c>
       <c r="J83" t="n">
-        <v>-2.645</v>
+        <v>-3.055</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1172</v>
+        <v>-0.1339</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.93</v>
+        <v>-3.3475</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1995</v>
+        <v>-0.2175</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.9875</v>
+        <v>-5.4375</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5203</v>
+        <v>-0.5264</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.0075</v>
+        <v>-13.16</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.8359</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>20.8975</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.6898</v>
       </c>
       <c r="J88" t="n">
-        <v>18.0325</v>
+        <v>17.245</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.6898</v>
       </c>
       <c r="J89" t="n">
-        <v>18.0325</v>
+        <v>17.245</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3277</v>
+        <v>0.3341</v>
       </c>
       <c r="J90" t="n">
-        <v>8.192500000000001</v>
+        <v>8.352499999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.09</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2711</v>
+        <v>0.2818</v>
       </c>
       <c r="J91" t="n">
-        <v>6.7775</v>
+        <v>7.045</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3769</v>
+        <v>0.3656</v>
       </c>
       <c r="J92" t="n">
-        <v>10.1763</v>
+        <v>9.8712</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.0034</v>
+        <v>-0.012</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.324</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1722</v>
+        <v>-0.1894</v>
       </c>
       <c r="J94" t="n">
-        <v>-4.6494</v>
+        <v>-5.1138</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2514</v>
+        <v>-0.2682</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.7878</v>
+        <v>-7.2414</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4592</v>
+        <v>-0.4683</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.3984</v>
+        <v>-12.6441</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3277</v>
+        <v>1.3032</v>
       </c>
       <c r="J97" t="n">
-        <v>35.8479</v>
+        <v>35.1864</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.56</v>
       </c>
       <c r="I98" t="n">
-        <v>1.2152</v>
+        <v>1.1836</v>
       </c>
       <c r="J98" t="n">
-        <v>32.8104</v>
+        <v>31.9572</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>1.0026</v>
+        <v>0.9465</v>
       </c>
       <c r="J99" t="n">
-        <v>27.0702</v>
+        <v>25.5555</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.73</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.8536</v>
+        <v>-0.7825</v>
       </c>
       <c r="J100" t="n">
-        <v>-23.0472</v>
+        <v>-21.1275</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.9025</v>
+        <v>-0.8253</v>
       </c>
       <c r="J101" t="n">
-        <v>-24.3675</v>
+        <v>-22.2831</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.48</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1285</v>
+        <v>1.0879</v>
       </c>
       <c r="J102" t="n">
-        <v>39.4975</v>
+        <v>38.0765</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5448</v>
+        <v>0.5294</v>
       </c>
       <c r="J103" t="n">
-        <v>19.068</v>
+        <v>18.529</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4208</v>
+        <v>0.4165</v>
       </c>
       <c r="J104" t="n">
-        <v>14.728</v>
+        <v>14.5775</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.097</v>
+        <v>0.1129</v>
       </c>
       <c r="J105" t="n">
-        <v>3.395</v>
+        <v>3.9515</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3614</v>
+        <v>-0.3442</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.649</v>
+        <v>-12.047</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9264</v>
+        <v>0.8747</v>
       </c>
       <c r="J107" t="n">
-        <v>32.424</v>
+        <v>30.6145</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4061</v>
+        <v>0.4025</v>
       </c>
       <c r="J108" t="n">
-        <v>14.2135</v>
+        <v>14.0875</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1758</v>
+        <v>-0.1897</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.153</v>
+        <v>-6.6395</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3156</v>
+        <v>-0.3279</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.046</v>
+        <v>-11.4765</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3441</v>
+        <v>-0.3556</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.0435</v>
+        <v>-12.446</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.2046</v>
+        <v>1.1649</v>
       </c>
       <c r="J112" t="n">
-        <v>36.138</v>
+        <v>34.947</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2133</v>
+        <v>0.2198</v>
       </c>
       <c r="J113" t="n">
-        <v>6.399</v>
+        <v>6.594</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1823</v>
+        <v>0.1902</v>
       </c>
       <c r="J114" t="n">
-        <v>5.469</v>
+        <v>5.706</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1499</v>
+        <v>0.159</v>
       </c>
       <c r="J115" t="n">
-        <v>4.497</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8943</v>
+        <v>-0.8235</v>
       </c>
       <c r="J116" t="n">
-        <v>-26.829</v>
+        <v>-24.705</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9611</v>
+        <v>0.9121</v>
       </c>
       <c r="J117" t="n">
-        <v>28.833</v>
+        <v>27.363</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0325</v>
+        <v>0.0397</v>
       </c>
       <c r="J118" t="n">
-        <v>0.975</v>
+        <v>1.191</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0242</v>
+        <v>-0.028</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.726</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0541</v>
+        <v>-0.0613</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.623</v>
+        <v>-1.839</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3218</v>
+        <v>-0.3328</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.654</v>
+        <v>-9.984</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.84</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5835</v>
+        <v>1.5686</v>
       </c>
       <c r="J122" t="n">
-        <v>44.338</v>
+        <v>43.9208</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3143</v>
+        <v>0.3184</v>
       </c>
       <c r="J123" t="n">
-        <v>8.8004</v>
+        <v>8.9152</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0605</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="J124" t="n">
-        <v>1.694</v>
+        <v>2.1504</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2036</v>
+        <v>-0.196</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.7008</v>
+        <v>-5.488</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.82</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6101</v>
+        <v>-0.5699</v>
       </c>
       <c r="J126" t="n">
-        <v>-17.0828</v>
+        <v>-15.9572</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3771</v>
+        <v>0.3697</v>
       </c>
       <c r="J127" t="n">
-        <v>10.5588</v>
+        <v>10.3516</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1146</v>
+        <v>0.1165</v>
       </c>
       <c r="J128" t="n">
-        <v>3.2088</v>
+        <v>3.262</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1141</v>
+        <v>-0.1286</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.1948</v>
+        <v>-3.6008</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1667</v>
+        <v>-0.1826</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.6676</v>
+        <v>-5.1128</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4372</v>
+        <v>-0.4465</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.2416</v>
+        <v>-12.502</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.8762</v>
       </c>
       <c r="J132" t="n">
-        <v>25.218</v>
+        <v>23.6574</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.9123</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J133" t="n">
-        <v>24.6321</v>
+        <v>23.1228</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4905</v>
+        <v>0.4815</v>
       </c>
       <c r="J134" t="n">
-        <v>13.2435</v>
+        <v>13.0005</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2188</v>
+        <v>0.2314</v>
       </c>
       <c r="J135" t="n">
-        <v>5.9076</v>
+        <v>6.2478</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.178</v>
+        <v>-0.1687</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.806</v>
+        <v>-4.5549</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.138</v>
+        <v>0.1404</v>
       </c>
       <c r="J137" t="n">
-        <v>3.726</v>
+        <v>3.7908</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.98</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0277</v>
+        <v>-0.0364</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.7479</v>
+        <v>-0.9828</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1144</v>
+        <v>-0.1288</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.0888</v>
+        <v>-3.4776</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1464</v>
+        <v>-0.1618</v>
       </c>
       <c r="J140" t="n">
-        <v>-3.9528</v>
+        <v>-4.3686</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2776</v>
+        <v>-0.2926</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.4952</v>
+        <v>-7.9002</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6231</v>
+        <v>0.5927</v>
       </c>
       <c r="J142" t="n">
-        <v>14.9544</v>
+        <v>14.2248</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0994</v>
+        <v>0.0975</v>
       </c>
       <c r="J143" t="n">
-        <v>2.3856</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.75</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2721</v>
+        <v>-0.2883</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.5304</v>
+        <v>-6.9192</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.68</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3392</v>
+        <v>-0.3535</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.1408</v>
+        <v>-8.484</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3863</v>
+        <v>-0.3987</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.2712</v>
+        <v>-9.5688</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.02</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7406</v>
+        <v>1.7407</v>
       </c>
       <c r="J147" t="n">
-        <v>41.7744</v>
+        <v>41.7768</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6136</v>
+        <v>0.5971</v>
       </c>
       <c r="J148" t="n">
-        <v>14.7264</v>
+        <v>14.3304</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4405</v>
+        <v>0.4415</v>
       </c>
       <c r="J149" t="n">
-        <v>10.572</v>
+        <v>10.596</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3615</v>
+        <v>0.3697</v>
       </c>
       <c r="J150" t="n">
-        <v>8.676</v>
+        <v>8.8728</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.2066</v>
+        <v>-0.1888</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.9584</v>
+        <v>-4.5312</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6226</v>
+        <v>0.6044</v>
       </c>
       <c r="J152" t="n">
-        <v>21.791</v>
+        <v>21.154</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5731000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>20.587</v>
+        <v>20.0585</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0531</v>
+        <v>-0.0605</v>
       </c>
       <c r="J154" t="n">
-        <v>-1.8585</v>
+        <v>-2.1175</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2123</v>
+        <v>-0.2251</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.4305</v>
+        <v>-7.8785</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2822</v>
+        <v>-0.2942</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.877000000000001</v>
+        <v>-10.297</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.49</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1502</v>
+        <v>1.1095</v>
       </c>
       <c r="J157" t="n">
-        <v>40.257</v>
+        <v>38.8325</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6266</v>
+        <v>0.6009</v>
       </c>
       <c r="J158" t="n">
-        <v>21.931</v>
+        <v>21.0315</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0281</v>
+        <v>-0.0193</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.9835</v>
+        <v>-0.6755</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1962</v>
+        <v>-0.1908</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.867</v>
+        <v>-6.678</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2931</v>
+        <v>-0.2825</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.2585</v>
+        <v>-9.887499999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9434</v>
+        <v>0.8756</v>
       </c>
       <c r="J162" t="n">
-        <v>28.302</v>
+        <v>26.268</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2471</v>
+        <v>0.2507</v>
       </c>
       <c r="J163" t="n">
-        <v>7.413</v>
+        <v>7.521</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.05</v>
       </c>
       <c r="I164" t="n">
-        <v>0.1865</v>
+        <v>0.193</v>
       </c>
       <c r="J164" t="n">
-        <v>5.595</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0098</v>
+        <v>-0.0066</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.294</v>
+        <v>-0.198</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.78</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6869</v>
+        <v>-0.6431</v>
       </c>
       <c r="J166" t="n">
-        <v>-20.607</v>
+        <v>-19.293</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3359</v>
+        <v>0.3396</v>
       </c>
       <c r="J167" t="n">
-        <v>10.077</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3359</v>
+        <v>0.3396</v>
       </c>
       <c r="J168" t="n">
-        <v>10.077</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2782</v>
+        <v>0.2849</v>
       </c>
       <c r="J169" t="n">
-        <v>8.346</v>
+        <v>8.547000000000001</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1978</v>
+        <v>0.2073</v>
       </c>
       <c r="J170" t="n">
-        <v>5.934</v>
+        <v>6.219</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3681</v>
+        <v>-0.3779</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.043</v>
+        <v>-11.337</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>0.72</v>
+        <v>0.6947</v>
       </c>
       <c r="J172" t="n">
-        <v>21.6</v>
+        <v>20.841</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="J173" t="n">
-        <v>2.142</v>
+        <v>2.373</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0751</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.253</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1659</v>
+        <v>-0.1795</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.977</v>
+        <v>-5.385</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.62</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.41</v>
+        <v>-0.419</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.3</v>
+        <v>-12.57</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5072</v>
+        <v>0.517</v>
       </c>
       <c r="J177" t="n">
-        <v>15.216</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4401</v>
+        <v>0.4533</v>
       </c>
       <c r="J178" t="n">
-        <v>13.203</v>
+        <v>13.599</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4061</v>
+        <v>0.4207</v>
       </c>
       <c r="J179" t="n">
-        <v>12.183</v>
+        <v>12.621</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1039</v>
+        <v>0.1223</v>
       </c>
       <c r="J180" t="n">
-        <v>3.117</v>
+        <v>3.669</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.05</v>
       </c>
       <c r="I181" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0898</v>
       </c>
       <c r="J181" t="n">
-        <v>2.172</v>
+        <v>2.694</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.8081</v>
+        <v>0.7631</v>
       </c>
       <c r="J182" t="n">
-        <v>21.8187</v>
+        <v>20.6037</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5933</v>
+        <v>0.573</v>
       </c>
       <c r="J183" t="n">
-        <v>16.0191</v>
+        <v>15.471</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3946</v>
+        <v>0.3926</v>
       </c>
       <c r="J184" t="n">
-        <v>10.6542</v>
+        <v>10.6002</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2852</v>
+        <v>0.2915</v>
       </c>
       <c r="J185" t="n">
-        <v>7.7004</v>
+        <v>7.8705</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0965</v>
+        <v>0.1125</v>
       </c>
       <c r="J186" t="n">
-        <v>2.6055</v>
+        <v>3.0375</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5972</v>
+        <v>0.5766</v>
       </c>
       <c r="J187" t="n">
-        <v>16.1244</v>
+        <v>15.5682</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0334</v>
+        <v>-0.0408</v>
       </c>
       <c r="J188" t="n">
-        <v>-0.9018</v>
+        <v>-1.1016</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.1086</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.5974</v>
+        <v>-2.9322</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.141</v>
+        <v>-0.1549</v>
       </c>
       <c r="J190" t="n">
-        <v>-3.807</v>
+        <v>-4.1823</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.73</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3032</v>
+        <v>-0.3163</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.186400000000001</v>
+        <v>-8.540100000000001</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8547</v>
+        <v>0.8184</v>
       </c>
       <c r="J192" t="n">
-        <v>24.7863</v>
+        <v>23.7336</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.226</v>
+        <v>0.2379</v>
       </c>
       <c r="J193" t="n">
-        <v>6.554</v>
+        <v>6.8991</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.0982</v>
+        <v>0.1119</v>
       </c>
       <c r="J194" t="n">
-        <v>2.8478</v>
+        <v>3.2451</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0738</v>
+        <v>0.0872</v>
       </c>
       <c r="J195" t="n">
-        <v>2.1402</v>
+        <v>2.5288</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.96</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0755</v>
+        <v>-0.082</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.1895</v>
+        <v>-2.378</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4265</v>
+        <v>0.4085</v>
       </c>
       <c r="J197" t="n">
-        <v>12.3685</v>
+        <v>11.8465</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0665</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J198" t="n">
-        <v>1.9285</v>
+        <v>1.9604</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1863</v>
+        <v>-0.1929</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.4027</v>
+        <v>-5.5941</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.306</v>
+        <v>-0.3056</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.874000000000001</v>
+        <v>-8.862399999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7084</v>
+        <v>-0.6673</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.5436</v>
+        <v>-19.3517</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6314</v>
+        <v>0.6109</v>
       </c>
       <c r="J202" t="n">
-        <v>22.099</v>
+        <v>21.3815</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.15</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3427</v>
+        <v>0.3445</v>
       </c>
       <c r="J203" t="n">
-        <v>11.9945</v>
+        <v>12.0575</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1351</v>
+        <v>-0.1476</v>
       </c>
       <c r="J204" t="n">
-        <v>-4.7285</v>
+        <v>-5.166</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1784</v>
+        <v>-0.1916</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.244</v>
+        <v>-6.706</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2198</v>
+        <v>-0.2331</v>
       </c>
       <c r="J206" t="n">
-        <v>-7.693</v>
+        <v>-8.1585</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.711</v>
+        <v>0.6736</v>
       </c>
       <c r="J207" t="n">
-        <v>24.885</v>
+        <v>23.576</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4058</v>
+        <v>0.4001</v>
       </c>
       <c r="J208" t="n">
-        <v>14.203</v>
+        <v>14.0035</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1793</v>
+        <v>0.1882</v>
       </c>
       <c r="J209" t="n">
-        <v>6.2755</v>
+        <v>6.587</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1793</v>
+        <v>0.1882</v>
       </c>
       <c r="J210" t="n">
-        <v>6.2755</v>
+        <v>6.587</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1876</v>
+        <v>-0.1848</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.566</v>
+        <v>-6.468</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1589</v>
+        <v>0.1557</v>
       </c>
       <c r="J212" t="n">
-        <v>4.2903</v>
+        <v>4.2039</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0848</v>
+        <v>-0.0999</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.2896</v>
+        <v>-2.6973</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0848</v>
+        <v>-0.0999</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.2896</v>
+        <v>-2.6973</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2891</v>
+        <v>-0.3053</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.8057</v>
+        <v>-8.2431</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3839</v>
+        <v>-0.3968</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.3653</v>
+        <v>-10.7136</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.65</v>
       </c>
       <c r="I217" t="n">
-        <v>1.322</v>
+        <v>1.2982</v>
       </c>
       <c r="J217" t="n">
-        <v>35.694</v>
+        <v>35.0514</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1344</v>
+        <v>1.098</v>
       </c>
       <c r="J218" t="n">
-        <v>30.6288</v>
+        <v>29.646</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4818</v>
+        <v>0.4755</v>
       </c>
       <c r="J219" t="n">
-        <v>13.0086</v>
+        <v>12.8385</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2245</v>
+        <v>-0.2106</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.0615</v>
+        <v>-5.6862</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4957</v>
+        <v>-0.4628</v>
       </c>
       <c r="J221" t="n">
-        <v>-13.3839</v>
+        <v>-12.4956</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.73</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2349</v>
+        <v>-0.2634</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.4631</v>
+        <v>-5.0046</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.64</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3289</v>
+        <v>-0.3525</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.2491</v>
+        <v>-6.6975</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3861</v>
+        <v>-0.4068</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.3359</v>
+        <v>-7.7292</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.48</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4762</v>
+        <v>-0.4917</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.047800000000001</v>
+        <v>-9.3423</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.38</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.572</v>
+        <v>-0.5803</v>
       </c>
       <c r="J226" t="n">
-        <v>-10.868</v>
+        <v>-11.0257</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.87</v>
       </c>
       <c r="I227" t="n">
-        <v>1.506</v>
+        <v>1.5055</v>
       </c>
       <c r="J227" t="n">
-        <v>28.614</v>
+        <v>28.6045</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.82</v>
       </c>
       <c r="I228" t="n">
-        <v>1.4504</v>
+        <v>1.4467</v>
       </c>
       <c r="J228" t="n">
-        <v>27.5576</v>
+        <v>27.4873</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2706</v>
+        <v>1.2552</v>
       </c>
       <c r="J229" t="n">
-        <v>24.1414</v>
+        <v>23.8488</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.5</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0889</v>
+        <v>1.0579</v>
       </c>
       <c r="J230" t="n">
-        <v>20.6891</v>
+        <v>20.1001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2227</v>
+        <v>-0.1897</v>
       </c>
       <c r="J231" t="n">
-        <v>-4.2313</v>
+        <v>-3.6043</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8899</v>
+        <v>0.8325</v>
       </c>
       <c r="J232" t="n">
-        <v>30.2566</v>
+        <v>28.305</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.25</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6998</v>
+        <v>0.6657999999999999</v>
       </c>
       <c r="J233" t="n">
-        <v>23.7932</v>
+        <v>22.6372</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.22</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6266</v>
+        <v>0.6009</v>
       </c>
       <c r="J234" t="n">
-        <v>21.3044</v>
+        <v>20.4306</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5522</v>
+        <v>0.5345</v>
       </c>
       <c r="J235" t="n">
-        <v>18.7748</v>
+        <v>18.173</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.1213</v>
+        <v>-1.018</v>
       </c>
       <c r="J236" t="n">
-        <v>-38.1242</v>
+        <v>-34.612</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.1</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2549</v>
+        <v>0.2587</v>
       </c>
       <c r="J237" t="n">
-        <v>8.666600000000001</v>
+        <v>8.7958</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0431</v>
+        <v>0.0472</v>
       </c>
       <c r="J238" t="n">
-        <v>1.4654</v>
+        <v>1.6048</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.93</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.0968</v>
+        <v>-0.109</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.2912</v>
+        <v>-3.706</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.4438</v>
+        <v>-4.9028</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1307</v>
+        <v>-0.1442</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.4438</v>
+        <v>-4.9028</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2693</v>
+        <v>1.2406</v>
       </c>
       <c r="J242" t="n">
-        <v>31.7325</v>
+        <v>31.015</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0649</v>
+        <v>1.018</v>
       </c>
       <c r="J243" t="n">
-        <v>26.6225</v>
+        <v>25.45</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3856</v>
+        <v>0.3864</v>
       </c>
       <c r="J244" t="n">
-        <v>9.640000000000001</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.02</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0484</v>
+        <v>0.0683</v>
       </c>
       <c r="J245" t="n">
-        <v>1.21</v>
+        <v>1.7075</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.79</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6999</v>
+        <v>-0.6475</v>
       </c>
       <c r="J246" t="n">
-        <v>-17.4975</v>
+        <v>-16.1875</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.13</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3289</v>
+        <v>0.3261</v>
       </c>
       <c r="J247" t="n">
-        <v>8.2225</v>
+        <v>8.1525</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.01</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0523</v>
+        <v>0.0538</v>
       </c>
       <c r="J248" t="n">
-        <v>1.3075</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0523</v>
+        <v>0.0538</v>
       </c>
       <c r="J249" t="n">
-        <v>1.3075</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.75</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2796</v>
+        <v>-0.2942</v>
       </c>
       <c r="J250" t="n">
-        <v>-6.99</v>
+        <v>-7.355</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2893</v>
+        <v>-0.3036</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.2325</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7834</v>
+        <v>0.7416</v>
       </c>
       <c r="J252" t="n">
-        <v>21.9352</v>
+        <v>20.7648</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.27</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7363</v>
+        <v>0.7002</v>
       </c>
       <c r="J253" t="n">
-        <v>20.6164</v>
+        <v>19.6056</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6408</v>
+        <v>0.6156</v>
       </c>
       <c r="J254" t="n">
-        <v>17.9424</v>
+        <v>17.2368</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2553</v>
+        <v>0.2639</v>
       </c>
       <c r="J255" t="n">
-        <v>7.1484</v>
+        <v>7.3892</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.363</v>
+        <v>-0.3453</v>
       </c>
       <c r="J256" t="n">
-        <v>-10.164</v>
+        <v>-9.6684</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.07</v>
       </c>
       <c r="I257" t="n">
-        <v>0.22</v>
+        <v>0.2181</v>
       </c>
       <c r="J257" t="n">
-        <v>6.16</v>
+        <v>6.1068</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.1225</v>
+        <v>-0.138</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.43</v>
+        <v>-3.864</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.87</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1536</v>
+        <v>-0.17</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.3008</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1942</v>
+        <v>-0.211</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.4376</v>
+        <v>-5.908</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.72</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3022</v>
+        <v>-0.3174</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.461600000000001</v>
+        <v>-8.8872</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3917</v>
+        <v>0.3926</v>
       </c>
       <c r="J262" t="n">
-        <v>14.1012</v>
+        <v>14.1336</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.15</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2644</v>
+        <v>0.2715</v>
       </c>
       <c r="J263" t="n">
-        <v>9.5184</v>
+        <v>9.773999999999999</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.04</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0891</v>
+        <v>0.0978</v>
       </c>
       <c r="J264" t="n">
-        <v>3.2076</v>
+        <v>3.5208</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0204</v>
+        <v>-0.0251</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.9036</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4563</v>
+        <v>-0.4631</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.4268</v>
+        <v>-16.6716</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.36</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4857</v>
+        <v>0.4923</v>
       </c>
       <c r="J267" t="n">
-        <v>17.4852</v>
+        <v>17.7228</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.32</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4386</v>
+        <v>0.4477</v>
       </c>
       <c r="J268" t="n">
-        <v>15.7896</v>
+        <v>16.1172</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.202</v>
+        <v>0.218</v>
       </c>
       <c r="J269" t="n">
-        <v>7.272</v>
+        <v>7.848</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1678</v>
+        <v>-0.1784</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.0408</v>
+        <v>-6.4224</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.84</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2101</v>
+        <v>-0.2211</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.5636</v>
+        <v>-7.9596</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.9258</v>
+        <v>0.8623</v>
       </c>
       <c r="J272" t="n">
-        <v>32.403</v>
+        <v>30.1805</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8558</v>
+        <v>0.8006</v>
       </c>
       <c r="J273" t="n">
-        <v>29.953</v>
+        <v>28.021</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0349</v>
+        <v>0.0461</v>
       </c>
       <c r="J274" t="n">
-        <v>1.2215</v>
+        <v>1.6135</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.221</v>
+        <v>-0.2167</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.735</v>
+        <v>-7.5845</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5677</v>
+        <v>-0.535</v>
       </c>
       <c r="J276" t="n">
-        <v>-19.8695</v>
+        <v>-18.725</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.2</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4325</v>
+        <v>0.4292</v>
       </c>
       <c r="J277" t="n">
-        <v>15.1375</v>
+        <v>15.022</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.13</v>
       </c>
       <c r="I278" t="n">
-        <v>0.301</v>
+        <v>0.3058</v>
       </c>
       <c r="J278" t="n">
-        <v>10.535</v>
+        <v>10.703</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0221</v>
+        <v>-0.0264</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.7735</v>
+        <v>-0.924</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0779</v>
+        <v>-0.0876</v>
       </c>
       <c r="J280" t="n">
-        <v>-2.7265</v>
+        <v>-3.066</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2109</v>
+        <v>-0.224</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.3815</v>
+        <v>-7.84</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4585</v>
+        <v>0.4482</v>
       </c>
       <c r="J282" t="n">
-        <v>13.2965</v>
+        <v>12.9978</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.01</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0483</v>
+        <v>0.0509</v>
       </c>
       <c r="J283" t="n">
-        <v>1.4007</v>
+        <v>1.4761</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.059</v>
+        <v>-0.0693</v>
       </c>
       <c r="J284" t="n">
-        <v>-1.711</v>
+        <v>-2.0097</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.8</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2323</v>
+        <v>-0.2472</v>
       </c>
       <c r="J285" t="n">
-        <v>-6.7367</v>
+        <v>-7.1688</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2816</v>
+        <v>-0.2957</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.166399999999999</v>
+        <v>-8.5753</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.64</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3338</v>
+        <v>1.3065</v>
       </c>
       <c r="J287" t="n">
-        <v>38.6802</v>
+        <v>37.8885</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9453</v>
+        <v>0.8847</v>
       </c>
       <c r="J288" t="n">
-        <v>27.4137</v>
+        <v>25.6563</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.06</v>
+        <v>0.0764</v>
       </c>
       <c r="J289" t="n">
-        <v>1.74</v>
+        <v>2.2156</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3614</v>
+        <v>-0.3442</v>
       </c>
       <c r="J290" t="n">
-        <v>-10.4806</v>
+        <v>-9.9818</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6106</v>
+        <v>-0.5702</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.7074</v>
+        <v>-16.5358</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.17</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3683</v>
+        <v>0.3711</v>
       </c>
       <c r="J292" t="n">
-        <v>13.2588</v>
+        <v>13.3596</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2544</v>
+        <v>0.2631</v>
       </c>
       <c r="J293" t="n">
-        <v>9.1584</v>
+        <v>9.4716</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1943</v>
+        <v>0.2048</v>
       </c>
       <c r="J294" t="n">
-        <v>6.9948</v>
+        <v>7.3728</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.03</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0848</v>
+        <v>0.0951</v>
       </c>
       <c r="J295" t="n">
-        <v>3.0528</v>
+        <v>3.4236</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.88</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.1622</v>
+        <v>-0.174</v>
       </c>
       <c r="J296" t="n">
-        <v>-5.8392</v>
+        <v>-6.264</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.8129</v>
+        <v>0.7664</v>
       </c>
       <c r="J297" t="n">
-        <v>29.2644</v>
+        <v>27.5904</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.67</v>
+        <v>0.6405</v>
       </c>
       <c r="J298" t="n">
-        <v>24.12</v>
+        <v>23.058</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3969</v>
+        <v>0.3941</v>
       </c>
       <c r="J299" t="n">
-        <v>14.2884</v>
+        <v>14.1876</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.13</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3969</v>
+        <v>0.3941</v>
       </c>
       <c r="J300" t="n">
-        <v>14.2884</v>
+        <v>14.1876</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.4163</v>
+        <v>-0.3953</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.9868</v>
+        <v>-14.2308</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/5463/event_5463_evp_summary.xlsx
+++ b/database/event/5463/event_5463_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.6342</v>
+        <v>6.3928</v>
       </c>
       <c r="C2" t="n">
-        <v>2.0399</v>
+        <v>1.9657</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3958</v>
+        <v>2.3064</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6342</v>
+        <v>6.3928</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1859</v>
+        <v>4.0025</v>
       </c>
       <c r="G2" t="n">
-        <v>2.4483</v>
+        <v>2.3903</v>
       </c>
       <c r="H2" t="n">
-        <v>8.9168</v>
+        <v>8.5846</v>
       </c>
       <c r="I2" t="n">
-        <v>4.815</v>
+        <v>4.82</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4483</v>
+        <v>2.3903</v>
       </c>
       <c r="K2" t="n">
         <v>153</v>
@@ -529,7 +529,7 @@
         <v>146</v>
       </c>
       <c r="M2" t="n">
-        <v>7.263300000000001</v>
+        <v>7.2103</v>
       </c>
       <c r="N2" t="n">
         <v>299</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.0367</v>
+        <v>4.8439</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5487</v>
+        <v>1.4894</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6686</v>
+        <v>1.6008</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0367</v>
+        <v>4.8439</v>
       </c>
       <c r="F3" t="n">
-        <v>3.8811</v>
+        <v>3.7455</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1556</v>
+        <v>1.0984</v>
       </c>
       <c r="H3" t="n">
-        <v>7.9109</v>
+        <v>7.6197</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2718</v>
+        <v>4.2782</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1556</v>
+        <v>1.0984</v>
       </c>
       <c r="K3" t="n">
         <v>153</v>
@@ -575,7 +575,7 @@
         <v>146</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4274</v>
+        <v>5.3766</v>
       </c>
       <c r="N3" t="n">
         <v>299</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.8676</v>
+        <v>4.6145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.4967</v>
+        <v>1.4189</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5916</v>
+        <v>1.4963</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8676</v>
+        <v>4.6145</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0304</v>
+        <v>3.8658</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.7487</v>
       </c>
       <c r="H4" t="n">
-        <v>8.403600000000001</v>
+        <v>8.071199999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5379</v>
+        <v>4.5317</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8372000000000001</v>
+        <v>0.7487</v>
       </c>
       <c r="K4" t="n">
         <v>158</v>
@@ -621,7 +621,7 @@
         <v>56</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3751</v>
+        <v>5.2804</v>
       </c>
       <c r="N4" t="n">
         <v>214</v>
@@ -630,93 +630,93 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4246</v>
+        <v>4.4706</v>
       </c>
       <c r="C5" t="n">
-        <v>1.3605</v>
+        <v>1.3746</v>
       </c>
       <c r="D5" t="n">
-        <v>1.39</v>
+        <v>1.4308</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4246</v>
+        <v>4.4706</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1778</v>
+        <v>2.3953</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2468</v>
+        <v>2.0753</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5906</v>
+        <v>2.5503</v>
       </c>
       <c r="I5" t="n">
-        <v>3.0189</v>
+        <v>1.4319</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2468</v>
+        <v>2.0753</v>
       </c>
       <c r="K5" t="n">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="L5" t="n">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>4.2657</v>
+        <v>3.5072</v>
       </c>
       <c r="N5" t="n">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4087</v>
+        <v>4.2804</v>
       </c>
       <c r="C6" t="n">
-        <v>1.3556</v>
+        <v>1.3161</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3827</v>
+        <v>1.3441</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4087</v>
+        <v>4.2804</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2861</v>
+        <v>3.1282</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1226</v>
+        <v>1.1522</v>
       </c>
       <c r="H6" t="n">
-        <v>2.6486</v>
+        <v>5.3018</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4302</v>
+        <v>2.9768</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1226</v>
+        <v>1.1522</v>
       </c>
       <c r="K6" t="n">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="L6" t="n">
-        <v>146</v>
+        <v>171</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5528</v>
+        <v>4.129</v>
       </c>
       <c r="N6" t="n">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5011</v>
+        <v>3.4533</v>
       </c>
       <c r="C7" t="n">
-        <v>1.0765</v>
+        <v>1.0618</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9696</v>
+        <v>0.9674</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5011</v>
+        <v>3.4533</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2128</v>
+        <v>3.1432</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2883</v>
+        <v>0.3101</v>
       </c>
       <c r="H7" t="n">
-        <v>5.706</v>
+        <v>5.3583</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0812</v>
+        <v>3.0085</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2883</v>
+        <v>0.3101</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>171</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3695</v>
+        <v>3.3186</v>
       </c>
       <c r="N7" t="n">
         <v>285</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4819</v>
+        <v>3.3277</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0706</v>
+        <v>1.0232</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9608</v>
+        <v>0.9101</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4819</v>
+        <v>3.3277</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9032</v>
+        <v>2.8318</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5787</v>
+        <v>0.4959</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6845</v>
+        <v>4.1892</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5296</v>
+        <v>2.3521</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5787</v>
+        <v>0.4959</v>
       </c>
       <c r="K8" t="n">
         <v>228</v>
@@ -805,7 +805,7 @@
         <v>81</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1083</v>
+        <v>2.848</v>
       </c>
       <c r="N8" t="n">
         <v>309</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9123</v>
+        <v>2.8027</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8955</v>
+        <v>0.8618</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7015</v>
+        <v>0.671</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9123</v>
+        <v>2.8027</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2035</v>
+        <v>2.2153</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7088</v>
+        <v>0.5874</v>
       </c>
       <c r="H9" t="n">
-        <v>2.376</v>
+        <v>2.2153</v>
       </c>
       <c r="I9" t="n">
-        <v>1.283</v>
+        <v>1.2438</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7088</v>
+        <v>0.5874</v>
       </c>
       <c r="K9" t="n">
         <v>114</v>
@@ -851,7 +851,7 @@
         <v>171</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9918</v>
+        <v>1.8312</v>
       </c>
       <c r="N9" t="n">
         <v>285</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8653</v>
+        <v>2.7623</v>
       </c>
       <c r="C10" t="n">
-        <v>0.881</v>
+        <v>0.8493000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6801</v>
+        <v>0.6526</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8653</v>
+        <v>2.7623</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8653</v>
+        <v>2.7623</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5464</v>
+        <v>3.3802</v>
       </c>
       <c r="I10" t="n">
-        <v>3.5464</v>
+        <v>3.3802</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5464</v>
+        <v>3.3802</v>
       </c>
       <c r="N10" t="n">
         <v>189</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7258</v>
+        <v>2.6864</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8381</v>
+        <v>0.826</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6166</v>
+        <v>0.618</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7258</v>
+        <v>2.6864</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8428</v>
+        <v>2.8017</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.117</v>
+        <v>-0.1153</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4853</v>
+        <v>4.0761</v>
       </c>
       <c r="I11" t="n">
-        <v>2.422</v>
+        <v>2.2886</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.117</v>
+        <v>-0.1153</v>
       </c>
       <c r="K11" t="n">
         <v>158</v>
@@ -943,7 +943,7 @@
         <v>56</v>
       </c>
       <c r="M11" t="n">
-        <v>2.305</v>
+        <v>2.1733</v>
       </c>
       <c r="N11" t="n">
         <v>214</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6327</v>
+        <v>2.6684</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8095</v>
+        <v>0.8205</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5743</v>
+        <v>0.6098</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6327</v>
+        <v>2.6684</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0371</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6403</v>
+        <v>1.6313</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9923999999999999</v>
+        <v>1.0371</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5359</v>
+        <v>0.5823</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6403</v>
+        <v>1.6313</v>
       </c>
       <c r="K12" t="n">
         <v>153</v>
@@ -989,7 +989,7 @@
         <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1762</v>
+        <v>2.2136</v>
       </c>
       <c r="N12" t="n">
         <v>299</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4885</v>
+        <v>2.5719</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7652</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5086000000000001</v>
+        <v>0.5658</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4885</v>
+        <v>2.5719</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2857</v>
+        <v>2.406</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2028</v>
+        <v>0.1659</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6471</v>
+        <v>2.5905</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4294</v>
+        <v>1.4545</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2028</v>
+        <v>0.1659</v>
       </c>
       <c r="K13" t="n">
         <v>228</v>
@@ -1035,7 +1035,7 @@
         <v>81</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6322</v>
+        <v>1.6204</v>
       </c>
       <c r="N13" t="n">
         <v>309</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4117</v>
+        <v>2.3897</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7415</v>
+        <v>0.7348</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4737</v>
+        <v>0.4828</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4117</v>
+        <v>2.3897</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6302</v>
+        <v>1.6264</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7815</v>
+        <v>0.7633</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6302</v>
+        <v>1.6264</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8803</v>
+        <v>0.9132</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7815</v>
+        <v>0.7633</v>
       </c>
       <c r="K14" t="n">
         <v>114</v>
@@ -1081,7 +1081,7 @@
         <v>171</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6618</v>
+        <v>1.6765</v>
       </c>
       <c r="N14" t="n">
         <v>285</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3076</v>
+        <v>2.2842</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7095</v>
+        <v>0.7023</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4263</v>
+        <v>0.4348</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3076</v>
+        <v>2.2842</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3076</v>
+        <v>0.2071</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2.0771</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3257</v>
+        <v>0.2071</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3257</v>
+        <v>0.1163</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.0771</v>
       </c>
       <c r="K15" t="n">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M15" t="n">
-        <v>2.3257</v>
+        <v>2.1934</v>
       </c>
       <c r="N15" t="n">
-        <v>189</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2535</v>
+        <v>2.1949</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6929</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4016</v>
+        <v>0.3941</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2535</v>
+        <v>2.1949</v>
       </c>
       <c r="F16" t="n">
-        <v>0.152</v>
+        <v>2.1949</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1015</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.152</v>
+        <v>2.1949</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08210000000000001</v>
+        <v>2.1949</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1015</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="L16" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1836</v>
+        <v>2.1949</v>
       </c>
       <c r="N16" t="n">
-        <v>299</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4026</v>
+        <v>0.3791</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0282</v>
+        <v>-0.0441</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3092</v>
+        <v>1.233</v>
       </c>
       <c r="N17" t="n">
         <v>198</v>
@@ -1228,139 +1228,139 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9213</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2833</v>
+        <v>0.2568</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2048</v>
+        <v>-0.2253</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9213</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3137</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3924</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3137</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7094</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3924</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="L18" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.317</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>309</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>poizon</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2719</v>
+        <v>0.2152</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2217</v>
+        <v>-0.2869</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8843</v>
+        <v>0.7</v>
       </c>
       <c r="N19" t="n">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>poizon</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7753</v>
+        <v>0.6542</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2384</v>
+        <v>0.2012</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2713</v>
+        <v>-0.3078</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7753</v>
+        <v>0.6542</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7753</v>
+        <v>1.0948</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.4406</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7753</v>
+        <v>1.0948</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7753</v>
+        <v>0.6147</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.4406</v>
       </c>
       <c r="K20" t="n">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7753</v>
+        <v>0.1741</v>
       </c>
       <c r="N20" t="n">
-        <v>189</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1879</v>
+        <v>0.1729</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.346</v>
+        <v>-0.3497</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6111</v>
+        <v>0.5622</v>
       </c>
       <c r="N21" t="n">
         <v>129</v>
@@ -1412,170 +1412,170 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>misutaaa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5926</v>
+        <v>0.5163</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1822</v>
+        <v>0.1588</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3544</v>
+        <v>-0.3706</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5926</v>
+        <v>0.5163</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5926</v>
+        <v>0.6073</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.091</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5926</v>
+        <v>0.6073</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5926</v>
+        <v>0.341</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.091</v>
       </c>
       <c r="K22" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5926</v>
+        <v>0.25</v>
       </c>
       <c r="N22" t="n">
-        <v>129</v>
+        <v>214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5806</v>
+        <v>0.4903</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1785</v>
+        <v>0.1508</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3599</v>
+        <v>-0.3824</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5806</v>
+        <v>0.4903</v>
       </c>
       <c r="F23" t="n">
-        <v>1.063</v>
+        <v>0.4903</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4824</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.063</v>
+        <v>0.4903</v>
       </c>
       <c r="I23" t="n">
-        <v>0.574</v>
+        <v>0.4903</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4824</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="L23" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09159999999999996</v>
+        <v>0.4903</v>
       </c>
       <c r="N23" t="n">
-        <v>309</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TeSeS</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5049</v>
+        <v>0.374</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1552</v>
+        <v>0.115</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3944</v>
+        <v>-0.4354</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5049</v>
+        <v>0.374</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5049</v>
+        <v>0.8781</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.5041</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5049</v>
+        <v>0.8781</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5049</v>
+        <v>0.493</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.5041</v>
       </c>
       <c r="K24" t="n">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5049</v>
+        <v>-0.0111</v>
       </c>
       <c r="N24" t="n">
-        <v>133</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cadiaN</t>
+          <t>TeSeS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1488</v>
+        <v>0.1146</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4039</v>
+        <v>-0.436</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4839</v>
+        <v>0.3728</v>
       </c>
       <c r="N25" t="n">
         <v>133</v>
@@ -1596,93 +1596,93 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>misutaaa</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.447</v>
+        <v>0.3626</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1374</v>
+        <v>0.1115</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4207</v>
+        <v>-0.4406</v>
       </c>
       <c r="E26" t="n">
-        <v>0.447</v>
+        <v>0.3626</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5402</v>
+        <v>0.3626</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5402</v>
+        <v>0.3626</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2917</v>
+        <v>0.3626</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.09320000000000001</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="L26" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1985</v>
+        <v>0.3626</v>
       </c>
       <c r="N26" t="n">
-        <v>214</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>syrsoN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1315</v>
+        <v>0.1009</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4296</v>
+        <v>-0.4563</v>
       </c>
       <c r="E27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4276</v>
+        <v>0.3281</v>
       </c>
       <c r="N27" t="n">
-        <v>129</v>
+        <v>198</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1303</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4313</v>
+        <v>-0.4625</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4238</v>
+        <v>0.3145</v>
       </c>
       <c r="N28" t="n">
         <v>129</v>
@@ -1734,47 +1734,47 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>syrsoN</t>
+          <t>cadiaN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1167</v>
+        <v>0.0951</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4515</v>
+        <v>-0.4649</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>198</v>
+        <v>133</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3794</v>
+        <v>0.3093</v>
       </c>
       <c r="N29" t="n">
-        <v>198</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.3092</v>
+        <v>0.2287</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0951</v>
+        <v>0.0703</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4834</v>
+        <v>-0.5016</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3092</v>
+        <v>0.2287</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9887</v>
+        <v>0.8852</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.6795</v>
+        <v>-0.6565</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9887</v>
+        <v>0.8852</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5339</v>
+        <v>0.497</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6795</v>
+        <v>-0.6565</v>
       </c>
       <c r="K30" t="n">
         <v>158</v>
@@ -1817,7 +1817,7 @@
         <v>56</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1456</v>
+        <v>-0.1595</v>
       </c>
       <c r="N30" t="n">
         <v>214</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0456</v>
+        <v>0.0342</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5566</v>
+        <v>-0.5551</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1484</v>
+        <v>0.1112</v>
       </c>
       <c r="N31" t="n">
         <v>129</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0431</v>
+        <v>-0.0586</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6881</v>
+        <v>-0.6927</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1403</v>
+        <v>-0.1907</v>
       </c>
       <c r="N32" t="n">
         <v>133</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.107</v>
+        <v>-0.1084</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7826</v>
+        <v>-0.7664</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.348</v>
+        <v>-0.3526</v>
       </c>
       <c r="N33" t="n">
         <v>198</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1176</v>
+        <v>-0.1235</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7983</v>
+        <v>-0.7887</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.3825</v>
+        <v>-0.4016</v>
       </c>
       <c r="N34" t="n">
         <v>133</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1651</v>
+        <v>-0.1649</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8686</v>
+        <v>-0.8501</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5369</v>
+        <v>-0.5363</v>
       </c>
       <c r="N35" t="n">
         <v>189</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8161</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2859</v>
+        <v>-0.2509</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0475</v>
+        <v>-0.9776</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8161</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.5592</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.2569</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.5592</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.314</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.2569</v>
       </c>
       <c r="K36" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.5709</v>
       </c>
       <c r="N36" t="n">
-        <v>198</v>
+        <v>214</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>b0RUP</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2934</v>
+        <v>-0.2893</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0586</v>
+        <v>-1.0344</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9543</v>
+        <v>-0.9409</v>
       </c>
       <c r="N37" t="n">
-        <v>133</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>b0RUP</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0357</v>
+        <v>-0.9742</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3185</v>
+        <v>-0.2995</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0957</v>
+        <v>-1.0496</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0357</v>
+        <v>-0.9742</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.7417</v>
+        <v>-0.9742</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.294</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.7417</v>
+        <v>-0.9742</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4005</v>
+        <v>-0.9742</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.294</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L38" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6945</v>
+        <v>-0.9742</v>
       </c>
       <c r="N38" t="n">
-        <v>214</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3963</v>
+        <v>-1.4085</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4293</v>
+        <v>-0.4331</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2598</v>
+        <v>-1.2474</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3963</v>
+        <v>-1.4085</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.0504</v>
+        <v>-2.0103</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6541</v>
+        <v>0.6018</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.0504</v>
+        <v>-2.0103</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1072</v>
+        <v>-1.1287</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6541</v>
+        <v>0.6018</v>
       </c>
       <c r="K39" t="n">
         <v>114</v>
@@ -2231,7 +2231,7 @@
         <v>171</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.4530999999999999</v>
+        <v>-0.5269</v>
       </c>
       <c r="N39" t="n">
         <v>285</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5462</v>
+        <v>-0.5011</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4329</v>
+        <v>-1.3482</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7764</v>
+        <v>-1.6297</v>
       </c>
       <c r="N40" t="n">
         <v>189</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7862</v>
+        <v>-2.6958</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.8567</v>
+        <v>-0.8289</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8925</v>
+        <v>-1.8339</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7862</v>
+        <v>-2.6958</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.6236</v>
+        <v>-2.5147</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1626</v>
+        <v>-0.1811</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.6236</v>
+        <v>-2.5147</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4167</v>
+        <v>-1.4119</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1626</v>
+        <v>-0.1811</v>
       </c>
       <c r="K41" t="n">
         <v>228</v>
@@ -2323,7 +2323,7 @@
         <v>81</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.5793</v>
+        <v>-1.593</v>
       </c>
       <c r="N41" t="n">
         <v>309</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3284</v>
+        <v>0.2759</v>
       </c>
       <c r="J2" t="n">
-        <v>13.7928</v>
+        <v>11.5878</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.06</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1704</v>
+        <v>0.1332</v>
       </c>
       <c r="J3" t="n">
-        <v>7.1568</v>
+        <v>5.5944</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.02</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0736</v>
+        <v>0.0526</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0912</v>
+        <v>2.2092</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.89</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1581</v>
+        <v>-0.1381</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.6402</v>
+        <v>-5.8002</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.88</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1691</v>
+        <v>-0.1488</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.1022</v>
+        <v>-6.2496</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5879</v>
+        <v>0.5493</v>
       </c>
       <c r="J7" t="n">
-        <v>24.6918</v>
+        <v>23.0706</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5654</v>
+        <v>0.5262</v>
       </c>
       <c r="J8" t="n">
-        <v>23.7468</v>
+        <v>22.1004</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.13</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4015</v>
+        <v>0.3612</v>
       </c>
       <c r="J9" t="n">
-        <v>16.863</v>
+        <v>15.1704</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.1</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3264</v>
+        <v>0.2882</v>
       </c>
       <c r="J10" t="n">
-        <v>13.7088</v>
+        <v>12.1044</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.76</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6942</v>
+        <v>-0.662</v>
       </c>
       <c r="J11" t="n">
-        <v>-29.1564</v>
+        <v>-27.804</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>0.9</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1119</v>
+        <v>-0.0959</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3499</v>
+        <v>-2.0139</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2023</v>
+        <v>-0.187</v>
       </c>
       <c r="J13" t="n">
-        <v>-4.2483</v>
+        <v>-3.927</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.71</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3092</v>
+        <v>-0.2952</v>
       </c>
       <c r="J14" t="n">
-        <v>-6.4932</v>
+        <v>-6.1992</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.66</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.353</v>
+        <v>-0.3398</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.413</v>
+        <v>-7.1358</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.43</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5555</v>
+        <v>-0.5613</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.6655</v>
+        <v>-11.7873</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.77</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5457</v>
+        <v>1.5752</v>
       </c>
       <c r="J17" t="n">
-        <v>32.4597</v>
+        <v>33.0792</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.55</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1832</v>
+        <v>1.1996</v>
       </c>
       <c r="J18" t="n">
-        <v>24.8472</v>
+        <v>25.1916</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6667</v>
+        <v>0.6445</v>
       </c>
       <c r="J19" t="n">
-        <v>14.0007</v>
+        <v>13.5345</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.25</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6252</v>
+        <v>0.601</v>
       </c>
       <c r="J20" t="n">
-        <v>13.1292</v>
+        <v>12.621</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.16</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4265</v>
+        <v>0.3953</v>
       </c>
       <c r="J21" t="n">
-        <v>8.9565</v>
+        <v>8.301299999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.17</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3888</v>
+        <v>0.333</v>
       </c>
       <c r="J22" t="n">
-        <v>10.4976</v>
+        <v>8.991</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.14</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3345</v>
+        <v>0.2815</v>
       </c>
       <c r="J23" t="n">
-        <v>9.031499999999999</v>
+        <v>7.6005</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.06</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1751</v>
+        <v>0.1368</v>
       </c>
       <c r="J24" t="n">
-        <v>4.7277</v>
+        <v>3.6936</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.76</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2886</v>
+        <v>-0.27</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.7922</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.72</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3264</v>
+        <v>-0.3099</v>
       </c>
       <c r="J26" t="n">
-        <v>-8.812799999999999</v>
+        <v>-8.3673</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.39</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9618</v>
+        <v>0.9499</v>
       </c>
       <c r="J27" t="n">
-        <v>25.9686</v>
+        <v>25.6473</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.14</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4236</v>
+        <v>0.3836</v>
       </c>
       <c r="J28" t="n">
-        <v>11.4372</v>
+        <v>10.3572</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.05</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1875</v>
+        <v>0.1584</v>
       </c>
       <c r="J29" t="n">
-        <v>5.0625</v>
+        <v>4.2768</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.01</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0454</v>
+        <v>0.034</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2258</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.87</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4378</v>
+        <v>-0.3951</v>
       </c>
       <c r="J31" t="n">
-        <v>-11.8206</v>
+        <v>-10.6677</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.13</v>
       </c>
       <c r="I32" t="n">
-        <v>0.3362</v>
+        <v>0.2845</v>
       </c>
       <c r="J32" t="n">
-        <v>8.741199999999999</v>
+        <v>7.397</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.01</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0612</v>
+        <v>0.0426</v>
       </c>
       <c r="J33" t="n">
-        <v>1.5912</v>
+        <v>1.1076</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.9</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.139</v>
+        <v>-0.1217</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.614</v>
+        <v>-3.1642</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.88</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1604</v>
+        <v>-0.1421</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.1704</v>
+        <v>-3.6946</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.54</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.48</v>
+        <v>-0.4776</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.48</v>
+        <v>-12.4176</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.45</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8934</v>
+        <v>0.8782</v>
       </c>
       <c r="J37" t="n">
-        <v>23.2284</v>
+        <v>22.8332</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.39</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8079</v>
+        <v>0.792</v>
       </c>
       <c r="J38" t="n">
-        <v>21.0054</v>
+        <v>20.592</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4711</v>
+        <v>0.4465</v>
       </c>
       <c r="J39" t="n">
-        <v>12.2486</v>
+        <v>11.609</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.93</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2921</v>
+        <v>-0.2523</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.5946</v>
+        <v>-6.5598</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.92</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3205</v>
+        <v>-0.2798</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.333</v>
+        <v>-7.2748</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.25</v>
       </c>
       <c r="I42" t="n">
-        <v>0.501</v>
+        <v>0.4642</v>
       </c>
       <c r="J42" t="n">
-        <v>15.03</v>
+        <v>13.926</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.01</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0458</v>
+        <v>0.0307</v>
       </c>
       <c r="J43" t="n">
-        <v>1.374</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.91</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1336</v>
+        <v>-0.1148</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.008</v>
+        <v>-3.444</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.87</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1782</v>
+        <v>-0.1579</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.346</v>
+        <v>-4.737</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.85</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1995</v>
+        <v>-0.1789</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.985</v>
+        <v>-5.367</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.35</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7642</v>
+        <v>0.7481</v>
       </c>
       <c r="J47" t="n">
-        <v>22.926</v>
+        <v>22.443</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5619</v>
+        <v>0.5512</v>
       </c>
       <c r="J48" t="n">
-        <v>16.857</v>
+        <v>16.536</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.08</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2723</v>
+        <v>0.2376</v>
       </c>
       <c r="J49" t="n">
-        <v>8.169</v>
+        <v>7.128</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0157</v>
+        <v>-0.0111</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.471</v>
+        <v>-0.333</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.85</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.489</v>
+        <v>-0.4473</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.67</v>
+        <v>-13.419</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.17</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4789</v>
+        <v>0.4533</v>
       </c>
       <c r="J52" t="n">
-        <v>13.8881</v>
+        <v>13.1457</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.14</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4215</v>
+        <v>0.3829</v>
       </c>
       <c r="J53" t="n">
-        <v>12.2235</v>
+        <v>11.1041</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.12</v>
       </c>
       <c r="I54" t="n">
-        <v>0.3741</v>
+        <v>0.3353</v>
       </c>
       <c r="J54" t="n">
-        <v>10.8489</v>
+        <v>9.723699999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.07</v>
       </c>
       <c r="I55" t="n">
-        <v>0.245</v>
+        <v>0.2119</v>
       </c>
       <c r="J55" t="n">
-        <v>7.105</v>
+        <v>6.1451</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.99</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.075</v>
+        <v>-0.0549</v>
       </c>
       <c r="J56" t="n">
-        <v>-2.175</v>
+        <v>-1.5921</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4912</v>
+        <v>0.4514</v>
       </c>
       <c r="J57" t="n">
-        <v>14.2448</v>
+        <v>13.0906</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.01</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0475</v>
+        <v>0.0317</v>
       </c>
       <c r="J58" t="n">
-        <v>1.3775</v>
+        <v>0.9193</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1209</v>
+        <v>-0.103</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.5061</v>
+        <v>-2.987</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.86</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1879</v>
+        <v>-0.1675</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.4491</v>
+        <v>-4.8575</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2493</v>
+        <v>-0.2293</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.2297</v>
+        <v>-6.6497</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.1</v>
       </c>
       <c r="I62" t="n">
-        <v>0.215</v>
+        <v>0.199</v>
       </c>
       <c r="J62" t="n">
-        <v>5.805</v>
+        <v>5.373</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.03</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0919</v>
+        <v>0.0769</v>
       </c>
       <c r="J63" t="n">
-        <v>2.4813</v>
+        <v>2.0763</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>0.92</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.1169</v>
+        <v>-0.1008</v>
       </c>
       <c r="J64" t="n">
-        <v>-3.1563</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.85</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1926</v>
+        <v>-0.1731</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.2002</v>
+        <v>-4.6737</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.61</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4197</v>
+        <v>-0.4105</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.3319</v>
+        <v>-11.0835</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3598</v>
+        <v>0.3006</v>
       </c>
       <c r="J67" t="n">
-        <v>9.714600000000001</v>
+        <v>8.116199999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3365</v>
+        <v>0.2794</v>
       </c>
       <c r="J68" t="n">
-        <v>9.0855</v>
+        <v>7.5438</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.17</v>
       </c>
       <c r="I69" t="n">
-        <v>0.2649</v>
+        <v>0.2155</v>
       </c>
       <c r="J69" t="n">
-        <v>7.1523</v>
+        <v>5.8185</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.13</v>
       </c>
       <c r="I70" t="n">
-        <v>0.2142</v>
+        <v>0.1713</v>
       </c>
       <c r="J70" t="n">
-        <v>5.7834</v>
+        <v>4.6251</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>1.06</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1125</v>
+        <v>0.0851</v>
       </c>
       <c r="J71" t="n">
-        <v>3.0375</v>
+        <v>2.2977</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.63</v>
       </c>
       <c r="I72" t="n">
-        <v>1.0982</v>
+        <v>1.0897</v>
       </c>
       <c r="J72" t="n">
-        <v>27.455</v>
+        <v>27.2425</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.41</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8086</v>
+        <v>0.7971</v>
       </c>
       <c r="J73" t="n">
-        <v>20.215</v>
+        <v>19.9275</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.31</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6705</v>
+        <v>0.663</v>
       </c>
       <c r="J74" t="n">
-        <v>16.7625</v>
+        <v>16.575</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.23</v>
       </c>
       <c r="I75" t="n">
-        <v>0.5496</v>
+        <v>0.5471</v>
       </c>
       <c r="J75" t="n">
-        <v>13.74</v>
+        <v>13.6775</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.22</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5337</v>
+        <v>0.5309</v>
       </c>
       <c r="J76" t="n">
-        <v>13.3425</v>
+        <v>13.2725</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0946</v>
       </c>
       <c r="J77" t="n">
-        <v>2.3075</v>
+        <v>2.365</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.77</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.249</v>
+        <v>-0.2349</v>
       </c>
       <c r="J78" t="n">
-        <v>-6.225</v>
+        <v>-5.8725</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.71</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3066</v>
+        <v>-0.2936</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.665</v>
+        <v>-7.34</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5087</v>
+        <v>-0.5079</v>
       </c>
       <c r="J80" t="n">
-        <v>-12.7175</v>
+        <v>-12.6975</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.43</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5524</v>
+        <v>-0.5574</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.81</v>
+        <v>-13.935</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.07</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2308</v>
+        <v>0.1888</v>
       </c>
       <c r="J82" t="n">
-        <v>5.77</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1222</v>
+        <v>-0.1071</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.055</v>
+        <v>-2.6775</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1339</v>
+        <v>-0.1182</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.3475</v>
+        <v>-2.955</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2175</v>
+        <v>-0.1991</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.4375</v>
+        <v>-4.9775</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.48</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5264</v>
+        <v>-0.5295</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.16</v>
+        <v>-13.2375</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.32</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7907999999999999</v>
+        <v>0.7663</v>
       </c>
       <c r="J87" t="n">
-        <v>19.77</v>
+        <v>19.1575</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.6898</v>
+        <v>0.6602</v>
       </c>
       <c r="J88" t="n">
-        <v>17.245</v>
+        <v>16.505</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6898</v>
+        <v>0.6602</v>
       </c>
       <c r="J89" t="n">
-        <v>17.245</v>
+        <v>16.505</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3341</v>
+        <v>0.301</v>
       </c>
       <c r="J90" t="n">
-        <v>8.352499999999999</v>
+        <v>7.525</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.09</v>
       </c>
       <c r="I91" t="n">
-        <v>0.2818</v>
+        <v>0.2501</v>
       </c>
       <c r="J91" t="n">
-        <v>7.045</v>
+        <v>6.2525</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.14</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3656</v>
+        <v>0.314</v>
       </c>
       <c r="J92" t="n">
-        <v>9.8712</v>
+        <v>8.478</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>0.99</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.012</v>
+        <v>-0.0077</v>
       </c>
       <c r="J93" t="n">
-        <v>-0.324</v>
+        <v>-0.2079</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.85</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1894</v>
+        <v>-0.1709</v>
       </c>
       <c r="J94" t="n">
-        <v>-5.1138</v>
+        <v>-4.6143</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.77</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2682</v>
+        <v>-0.2494</v>
       </c>
       <c r="J95" t="n">
-        <v>-7.2414</v>
+        <v>-6.7338</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.55</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4683</v>
+        <v>-0.4641</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.6441</v>
+        <v>-12.5307</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.65</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3032</v>
+        <v>1.3237</v>
       </c>
       <c r="J97" t="n">
-        <v>35.1864</v>
+        <v>35.7399</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.56</v>
       </c>
       <c r="I98" t="n">
-        <v>1.1836</v>
+        <v>1.1979</v>
       </c>
       <c r="J98" t="n">
-        <v>31.9572</v>
+        <v>32.3433</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.4</v>
       </c>
       <c r="I99" t="n">
-        <v>0.9465</v>
+        <v>0.9351</v>
       </c>
       <c r="J99" t="n">
-        <v>25.5555</v>
+        <v>25.2477</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.73</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.7825</v>
+        <v>-0.7608</v>
       </c>
       <c r="J100" t="n">
-        <v>-21.1275</v>
+        <v>-20.5416</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.71</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.8253</v>
+        <v>-0.8077</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.2831</v>
+        <v>-21.8079</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.48</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0879</v>
+        <v>1.0983</v>
       </c>
       <c r="J102" t="n">
-        <v>38.0765</v>
+        <v>38.4405</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.19</v>
       </c>
       <c r="I103" t="n">
-        <v>0.5294</v>
+        <v>0.4923</v>
       </c>
       <c r="J103" t="n">
-        <v>18.529</v>
+        <v>17.2305</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.14</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4165</v>
+        <v>0.3796</v>
       </c>
       <c r="J104" t="n">
-        <v>14.5775</v>
+        <v>13.286</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.03</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1129</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J105" t="n">
-        <v>3.9515</v>
+        <v>3.213</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.91</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3442</v>
+        <v>-0.3025</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.047</v>
+        <v>-10.5875</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8747</v>
+        <v>0.8292</v>
       </c>
       <c r="J107" t="n">
-        <v>30.6145</v>
+        <v>29.022</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.18</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4025</v>
+        <v>0.3461</v>
       </c>
       <c r="J108" t="n">
-        <v>14.0875</v>
+        <v>12.1135</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.86</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1897</v>
+        <v>-0.1691</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.6395</v>
+        <v>-5.9185</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.72</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3279</v>
+        <v>-0.3116</v>
       </c>
       <c r="J110" t="n">
-        <v>-11.4765</v>
+        <v>-10.906</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3556</v>
+        <v>-0.3413</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.446</v>
+        <v>-11.9455</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.52</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1649</v>
+        <v>1.1815</v>
       </c>
       <c r="J112" t="n">
-        <v>34.947</v>
+        <v>35.445</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.06</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2198</v>
+        <v>0.1872</v>
       </c>
       <c r="J113" t="n">
-        <v>6.594</v>
+        <v>5.616</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1902</v>
+        <v>0.1601</v>
       </c>
       <c r="J114" t="n">
-        <v>5.706</v>
+        <v>4.803</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.04</v>
       </c>
       <c r="I115" t="n">
-        <v>0.159</v>
+        <v>0.1318</v>
       </c>
       <c r="J115" t="n">
-        <v>4.77</v>
+        <v>3.954</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.7</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.8235</v>
+        <v>-0.802</v>
       </c>
       <c r="J116" t="n">
-        <v>-24.705</v>
+        <v>-24.06</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9121</v>
+        <v>0.8663</v>
       </c>
       <c r="J117" t="n">
-        <v>27.363</v>
+        <v>25.989</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.01</v>
       </c>
       <c r="I118" t="n">
-        <v>0.0397</v>
+        <v>0.0276</v>
       </c>
       <c r="J118" t="n">
-        <v>1.191</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.99</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.028</v>
+        <v>-0.0199</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.84</v>
+        <v>-0.597</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.97</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0613</v>
+        <v>-0.0479</v>
       </c>
       <c r="J120" t="n">
-        <v>-1.839</v>
+        <v>-1.437</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.72</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3328</v>
+        <v>-0.3173</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.984</v>
+        <v>-9.519</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.84</v>
       </c>
       <c r="I122" t="n">
-        <v>1.5686</v>
+        <v>1.6148</v>
       </c>
       <c r="J122" t="n">
-        <v>43.9208</v>
+        <v>45.2144</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3184</v>
+        <v>0.2838</v>
       </c>
       <c r="J123" t="n">
-        <v>8.9152</v>
+        <v>7.9464</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0602</v>
       </c>
       <c r="J124" t="n">
-        <v>2.1504</v>
+        <v>1.6856</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.96</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.196</v>
+        <v>-0.1613</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.488</v>
+        <v>-4.5164</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.82</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5699</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="J126" t="n">
-        <v>-15.9572</v>
+        <v>-14.8904</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.15</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3697</v>
+        <v>0.3161</v>
       </c>
       <c r="J127" t="n">
-        <v>10.3516</v>
+        <v>8.8508</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.03</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1165</v>
+        <v>0.0867</v>
       </c>
       <c r="J128" t="n">
-        <v>3.262</v>
+        <v>2.4276</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.91</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1286</v>
+        <v>-0.1116</v>
       </c>
       <c r="J129" t="n">
-        <v>-3.6008</v>
+        <v>-3.1248</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.86</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1826</v>
+        <v>-0.1631</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.1128</v>
+        <v>-4.5668</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4465</v>
+        <v>-0.4402</v>
       </c>
       <c r="J131" t="n">
-        <v>-12.502</v>
+        <v>-12.3256</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.36</v>
       </c>
       <c r="I132" t="n">
-        <v>0.8762</v>
+        <v>0.8568</v>
       </c>
       <c r="J132" t="n">
-        <v>23.6574</v>
+        <v>23.1336</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.35</v>
       </c>
       <c r="I133" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.8355</v>
       </c>
       <c r="J133" t="n">
-        <v>23.1228</v>
+        <v>22.5585</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4815</v>
+        <v>0.446</v>
       </c>
       <c r="J134" t="n">
-        <v>13.0005</v>
+        <v>12.042</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.07</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2314</v>
+        <v>0.2014</v>
       </c>
       <c r="J135" t="n">
-        <v>6.2478</v>
+        <v>5.4378</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.97</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1687</v>
+        <v>-0.1372</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.5549</v>
+        <v>-3.7044</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.04</v>
       </c>
       <c r="I137" t="n">
-        <v>0.1404</v>
+        <v>0.1068</v>
       </c>
       <c r="J137" t="n">
-        <v>3.7908</v>
+        <v>2.8836</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.98</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0364</v>
+        <v>-0.0285</v>
       </c>
       <c r="J138" t="n">
-        <v>-0.9828</v>
+        <v>-0.7695</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.91</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1288</v>
+        <v>-0.1117</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.4776</v>
+        <v>-3.0159</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.88</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.1618</v>
+        <v>-0.1429</v>
       </c>
       <c r="J140" t="n">
-        <v>-4.3686</v>
+        <v>-3.8583</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.75</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2926</v>
+        <v>-0.2742</v>
       </c>
       <c r="J141" t="n">
-        <v>-7.9002</v>
+        <v>-7.4034</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.27</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5927</v>
+        <v>0.5403</v>
       </c>
       <c r="J142" t="n">
-        <v>14.2248</v>
+        <v>12.9672</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0975</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>2.34</v>
+        <v>1.7256</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.75</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2883</v>
+        <v>-0.27</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.9192</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.68</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3535</v>
+        <v>-0.3385</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.484</v>
+        <v>-8.124000000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.63</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3987</v>
+        <v>-0.3873</v>
       </c>
       <c r="J146" t="n">
-        <v>-9.5688</v>
+        <v>-9.295199999999999</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>2.02</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7407</v>
+        <v>1.7977</v>
       </c>
       <c r="J147" t="n">
-        <v>41.7768</v>
+        <v>43.1448</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.23</v>
       </c>
       <c r="I148" t="n">
-        <v>0.5971</v>
+        <v>0.5689</v>
       </c>
       <c r="J148" t="n">
-        <v>14.3304</v>
+        <v>13.6536</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.16</v>
       </c>
       <c r="I149" t="n">
-        <v>0.4415</v>
+        <v>0.4099</v>
       </c>
       <c r="J149" t="n">
-        <v>10.596</v>
+        <v>9.8376</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.13</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3697</v>
+        <v>0.3376</v>
       </c>
       <c r="J150" t="n">
-        <v>8.8728</v>
+        <v>8.102399999999999</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.97</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1888</v>
+        <v>-0.159</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.5312</v>
+        <v>-3.816</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6044</v>
+        <v>0.545</v>
       </c>
       <c r="J152" t="n">
-        <v>21.154</v>
+        <v>19.075</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.29</v>
       </c>
       <c r="I153" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5134</v>
       </c>
       <c r="J153" t="n">
-        <v>20.0585</v>
+        <v>17.969</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0605</v>
+        <v>-0.0473</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.1175</v>
+        <v>-1.6555</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.83</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2251</v>
+        <v>-0.2046</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.8785</v>
+        <v>-7.161</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.76</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.2942</v>
+        <v>-0.2762</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.297</v>
+        <v>-9.667</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.49</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1095</v>
+        <v>1.122</v>
       </c>
       <c r="J157" t="n">
-        <v>38.8325</v>
+        <v>39.27</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.22</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6009</v>
+        <v>0.5641</v>
       </c>
       <c r="J158" t="n">
-        <v>21.0315</v>
+        <v>19.7435</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0193</v>
+        <v>-0.0143</v>
       </c>
       <c r="J159" t="n">
-        <v>-0.6755</v>
+        <v>-0.5004999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1908</v>
+        <v>-0.1562</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.678</v>
+        <v>-5.467</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.93</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2825</v>
+        <v>-0.2423</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.887499999999999</v>
+        <v>-8.480499999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.34</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8756</v>
+        <v>0.8558</v>
       </c>
       <c r="J162" t="n">
-        <v>26.268</v>
+        <v>25.674</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.07</v>
       </c>
       <c r="I163" t="n">
-        <v>0.2507</v>
+        <v>0.2147</v>
       </c>
       <c r="J163" t="n">
-        <v>7.521</v>
+        <v>6.441</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.05</v>
       </c>
       <c r="I164" t="n">
-        <v>0.193</v>
+        <v>0.1614</v>
       </c>
       <c r="J164" t="n">
-        <v>5.79</v>
+        <v>4.842</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0066</v>
+        <v>-0.0039</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.198</v>
+        <v>-0.117</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.78</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6431</v>
+        <v>-0.607</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.293</v>
+        <v>-18.21</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3396</v>
+        <v>0.2867</v>
       </c>
       <c r="J167" t="n">
-        <v>10.188</v>
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3396</v>
+        <v>0.2867</v>
       </c>
       <c r="J168" t="n">
-        <v>10.188</v>
+        <v>8.601000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.12</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2849</v>
+        <v>0.2361</v>
       </c>
       <c r="J169" t="n">
-        <v>8.547000000000001</v>
+        <v>7.083</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.08</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2073</v>
+        <v>0.1663</v>
       </c>
       <c r="J170" t="n">
-        <v>6.219</v>
+        <v>4.989</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3779</v>
+        <v>-0.3659</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.337</v>
+        <v>-10.977</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.49</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6947</v>
+        <v>0.7403</v>
       </c>
       <c r="J172" t="n">
-        <v>20.841</v>
+        <v>22.209</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.03</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0791</v>
+        <v>0.0655</v>
       </c>
       <c r="J173" t="n">
-        <v>2.373</v>
+        <v>1.965</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.95</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.08550000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.565</v>
+        <v>-2.097</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.87</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1795</v>
+        <v>-0.159</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.385</v>
+        <v>-4.77</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.62</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.419</v>
+        <v>-0.4106</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.57</v>
+        <v>-12.318</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.4</v>
       </c>
       <c r="I177" t="n">
-        <v>0.517</v>
+        <v>0.4487</v>
       </c>
       <c r="J177" t="n">
-        <v>15.51</v>
+        <v>13.461</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.34</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4533</v>
+        <v>0.3884</v>
       </c>
       <c r="J178" t="n">
-        <v>13.599</v>
+        <v>11.652</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.31</v>
       </c>
       <c r="I179" t="n">
-        <v>0.4207</v>
+        <v>0.3581</v>
       </c>
       <c r="J179" t="n">
-        <v>12.621</v>
+        <v>10.743</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.07</v>
       </c>
       <c r="I180" t="n">
-        <v>0.1223</v>
+        <v>0.0935</v>
       </c>
       <c r="J180" t="n">
-        <v>3.669</v>
+        <v>2.805</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>1.05</v>
       </c>
       <c r="I181" t="n">
-        <v>0.0898</v>
+        <v>0.0665</v>
       </c>
       <c r="J181" t="n">
-        <v>2.694</v>
+        <v>1.995</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.3</v>
       </c>
       <c r="I182" t="n">
-        <v>0.7631</v>
+        <v>0.7349</v>
       </c>
       <c r="J182" t="n">
-        <v>20.6037</v>
+        <v>19.8423</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.21</v>
       </c>
       <c r="I183" t="n">
-        <v>0.573</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J183" t="n">
-        <v>15.471</v>
+        <v>14.4936</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.13</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3926</v>
+        <v>0.3562</v>
       </c>
       <c r="J184" t="n">
-        <v>10.6002</v>
+        <v>9.6174</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.09</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2915</v>
+        <v>0.2581</v>
       </c>
       <c r="J185" t="n">
-        <v>7.8705</v>
+        <v>6.9687</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.1125</v>
+        <v>0.0915</v>
       </c>
       <c r="J186" t="n">
-        <v>3.0375</v>
+        <v>2.4705</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.28</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5766</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>15.5682</v>
+        <v>14.0022</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.98</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.0408</v>
+        <v>-0.0315</v>
       </c>
       <c r="J188" t="n">
-        <v>-1.1016</v>
+        <v>-0.8505</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.93</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1086</v>
+        <v>-0.0916</v>
       </c>
       <c r="J189" t="n">
-        <v>-2.9322</v>
+        <v>-2.4732</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.89</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.1549</v>
+        <v>-0.1354</v>
       </c>
       <c r="J190" t="n">
-        <v>-4.1823</v>
+        <v>-3.6558</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.73</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3163</v>
+        <v>-0.2992</v>
       </c>
       <c r="J191" t="n">
-        <v>-8.540100000000001</v>
+        <v>-8.0784</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8184</v>
+        <v>0.7639</v>
       </c>
       <c r="J192" t="n">
-        <v>23.7336</v>
+        <v>22.1531</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.1</v>
       </c>
       <c r="I193" t="n">
-        <v>0.2379</v>
+        <v>0.1965</v>
       </c>
       <c r="J193" t="n">
-        <v>6.8991</v>
+        <v>5.6985</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.04</v>
       </c>
       <c r="I194" t="n">
-        <v>0.1119</v>
+        <v>0.0867</v>
       </c>
       <c r="J194" t="n">
-        <v>3.2451</v>
+        <v>2.5143</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.03</v>
       </c>
       <c r="I195" t="n">
-        <v>0.0872</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>2.5288</v>
+        <v>1.9169</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.96</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.082</v>
+        <v>-0.0663</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.378</v>
+        <v>-1.9227</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.12</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4085</v>
+        <v>0.3654</v>
       </c>
       <c r="J197" t="n">
-        <v>11.8465</v>
+        <v>10.5966</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.01</v>
       </c>
       <c r="I198" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0487</v>
       </c>
       <c r="J198" t="n">
-        <v>1.9604</v>
+        <v>1.4123</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1929</v>
+        <v>-0.1614</v>
       </c>
       <c r="J199" t="n">
-        <v>-5.5941</v>
+        <v>-4.6806</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3056</v>
+        <v>-0.2666</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.862399999999999</v>
+        <v>-7.7314</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.76</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6673</v>
+        <v>-0.6317</v>
       </c>
       <c r="J201" t="n">
-        <v>-19.3517</v>
+        <v>-18.3193</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.31</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6109</v>
+        <v>0.552</v>
       </c>
       <c r="J202" t="n">
-        <v>21.3815</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.15</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3445</v>
+        <v>0.291</v>
       </c>
       <c r="J203" t="n">
-        <v>12.0575</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.9</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.1476</v>
+        <v>-0.1279</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.166</v>
+        <v>-4.4765</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.86</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.1916</v>
+        <v>-0.171</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.706</v>
+        <v>-5.985</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2331</v>
+        <v>-0.2128</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.1585</v>
+        <v>-7.448</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.25</v>
       </c>
       <c r="I207" t="n">
-        <v>0.6736</v>
+        <v>0.6389</v>
       </c>
       <c r="J207" t="n">
-        <v>23.576</v>
+        <v>22.3615</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.13</v>
       </c>
       <c r="I208" t="n">
-        <v>0.4001</v>
+        <v>0.3602</v>
       </c>
       <c r="J208" t="n">
-        <v>14.0035</v>
+        <v>12.607</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.05</v>
       </c>
       <c r="I209" t="n">
-        <v>0.1882</v>
+        <v>0.1588</v>
       </c>
       <c r="J209" t="n">
-        <v>6.587</v>
+        <v>5.558</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.05</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1882</v>
+        <v>0.1588</v>
       </c>
       <c r="J210" t="n">
-        <v>6.587</v>
+        <v>5.558</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.96</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1848</v>
+        <v>-0.1505</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.468</v>
+        <v>-5.2675</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.04</v>
       </c>
       <c r="I212" t="n">
-        <v>0.1557</v>
+        <v>0.1215</v>
       </c>
       <c r="J212" t="n">
-        <v>4.2039</v>
+        <v>3.2805</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.93</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.0999</v>
+        <v>-0.0858</v>
       </c>
       <c r="J213" t="n">
-        <v>-2.6973</v>
+        <v>-2.3166</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.93</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0999</v>
+        <v>-0.0858</v>
       </c>
       <c r="J214" t="n">
-        <v>-2.6973</v>
+        <v>-2.3166</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.73</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3053</v>
+        <v>-0.2878</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.2431</v>
+        <v>-7.7706</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.63</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3968</v>
+        <v>-0.3851</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.7136</v>
+        <v>-10.3977</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.65</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2982</v>
+        <v>1.318</v>
       </c>
       <c r="J217" t="n">
-        <v>35.0514</v>
+        <v>35.586</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.098</v>
+        <v>1.1091</v>
       </c>
       <c r="J218" t="n">
-        <v>29.646</v>
+        <v>29.9457</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.17</v>
       </c>
       <c r="I219" t="n">
-        <v>0.4755</v>
+        <v>0.4422</v>
       </c>
       <c r="J219" t="n">
-        <v>12.8385</v>
+        <v>11.9394</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.96</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2106</v>
+        <v>-0.1766</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.6862</v>
+        <v>-4.7682</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.87</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4628</v>
+        <v>-0.4232</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.4956</v>
+        <v>-11.4264</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.73</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.2634</v>
+        <v>-0.2494</v>
       </c>
       <c r="J222" t="n">
-        <v>-5.0046</v>
+        <v>-4.7386</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.64</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.3525</v>
+        <v>-0.3446</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.6975</v>
+        <v>-6.5474</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.58</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.4068</v>
+        <v>-0.4009</v>
       </c>
       <c r="J224" t="n">
-        <v>-7.7292</v>
+        <v>-7.6171</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.48</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4917</v>
+        <v>-0.4897</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.3423</v>
+        <v>-9.3043</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.38</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.5803</v>
+        <v>-0.5883</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.0257</v>
+        <v>-11.1777</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.87</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5055</v>
+        <v>1.5383</v>
       </c>
       <c r="J227" t="n">
-        <v>28.6045</v>
+        <v>29.2277</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.82</v>
       </c>
       <c r="I228" t="n">
-        <v>1.4467</v>
+        <v>1.4762</v>
       </c>
       <c r="J228" t="n">
-        <v>27.4873</v>
+        <v>28.0478</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.66</v>
       </c>
       <c r="I229" t="n">
-        <v>1.2552</v>
+        <v>1.2773</v>
       </c>
       <c r="J229" t="n">
-        <v>23.8488</v>
+        <v>24.2687</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1.5</v>
       </c>
       <c r="I230" t="n">
-        <v>1.0579</v>
+        <v>1.0752</v>
       </c>
       <c r="J230" t="n">
-        <v>20.1001</v>
+        <v>20.4288</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.98</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1897</v>
+        <v>-0.1712</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.6043</v>
+        <v>-3.2528</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.33</v>
       </c>
       <c r="I232" t="n">
-        <v>0.8325</v>
+        <v>0.8086</v>
       </c>
       <c r="J232" t="n">
-        <v>28.305</v>
+        <v>27.4924</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.25</v>
       </c>
       <c r="I233" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.6315</v>
       </c>
       <c r="J233" t="n">
-        <v>22.6372</v>
+        <v>21.471</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.22</v>
       </c>
       <c r="I234" t="n">
-        <v>0.6009</v>
+        <v>0.5641</v>
       </c>
       <c r="J234" t="n">
-        <v>20.4306</v>
+        <v>19.1794</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>1.19</v>
       </c>
       <c r="I235" t="n">
-        <v>0.5345</v>
+        <v>0.4961</v>
       </c>
       <c r="J235" t="n">
-        <v>18.173</v>
+        <v>16.8674</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.61</v>
       </c>
       <c r="I236" t="n">
-        <v>-1.018</v>
+        <v>-1.0199</v>
       </c>
       <c r="J236" t="n">
-        <v>-34.612</v>
+        <v>-34.6766</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.1</v>
       </c>
       <c r="I237" t="n">
-        <v>0.2587</v>
+        <v>0.2113</v>
       </c>
       <c r="J237" t="n">
-        <v>8.7958</v>
+        <v>7.1842</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0472</v>
+        <v>0.0315</v>
       </c>
       <c r="J238" t="n">
-        <v>1.6048</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.93</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.109</v>
+        <v>-0.0919</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.706</v>
+        <v>-3.1246</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.9</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.9028</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.9</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1442</v>
+        <v>-0.125</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.9028</v>
+        <v>-4.25</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.6</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2406</v>
+        <v>1.2577</v>
       </c>
       <c r="J242" t="n">
-        <v>31.015</v>
+        <v>31.4425</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.44</v>
       </c>
       <c r="I243" t="n">
-        <v>1.018</v>
+        <v>1.0181</v>
       </c>
       <c r="J243" t="n">
-        <v>25.45</v>
+        <v>25.4525</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.13</v>
       </c>
       <c r="I244" t="n">
-        <v>0.3864</v>
+        <v>0.352</v>
       </c>
       <c r="J244" t="n">
-        <v>9.66</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.02</v>
       </c>
       <c r="I245" t="n">
-        <v>0.0683</v>
+        <v>0.0522</v>
       </c>
       <c r="J245" t="n">
-        <v>1.7075</v>
+        <v>1.305</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.79</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.6475</v>
+        <v>-0.615</v>
       </c>
       <c r="J246" t="n">
-        <v>-16.1875</v>
+        <v>-15.375</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.13</v>
       </c>
       <c r="I247" t="n">
-        <v>0.3261</v>
+        <v>0.274</v>
       </c>
       <c r="J247" t="n">
-        <v>8.1525</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.01</v>
       </c>
       <c r="I248" t="n">
-        <v>0.0538</v>
+        <v>0.0364</v>
       </c>
       <c r="J248" t="n">
-        <v>1.345</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.01</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0538</v>
+        <v>0.0364</v>
       </c>
       <c r="J249" t="n">
-        <v>1.345</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.75</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2942</v>
+        <v>-0.2758</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.355</v>
+        <v>-6.895</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.74</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3036</v>
+        <v>-0.2857</v>
       </c>
       <c r="J251" t="n">
-        <v>-7.59</v>
+        <v>-7.1425</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.7416</v>
+        <v>0.7123</v>
       </c>
       <c r="J252" t="n">
-        <v>20.7648</v>
+        <v>19.9444</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.27</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7002</v>
+        <v>0.6686</v>
       </c>
       <c r="J253" t="n">
-        <v>19.6056</v>
+        <v>18.7208</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.23</v>
       </c>
       <c r="I254" t="n">
-        <v>0.6156</v>
+        <v>0.5806</v>
       </c>
       <c r="J254" t="n">
-        <v>17.2368</v>
+        <v>16.2568</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>1.08</v>
       </c>
       <c r="I255" t="n">
-        <v>0.2639</v>
+        <v>0.2318</v>
       </c>
       <c r="J255" t="n">
-        <v>7.3892</v>
+        <v>6.4904</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.91</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3453</v>
+        <v>-0.3037</v>
       </c>
       <c r="J256" t="n">
-        <v>-9.6684</v>
+        <v>-8.5036</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.07</v>
       </c>
       <c r="I257" t="n">
-        <v>0.2181</v>
+        <v>0.1756</v>
       </c>
       <c r="J257" t="n">
-        <v>6.1068</v>
+        <v>4.9168</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.138</v>
+        <v>-0.1212</v>
       </c>
       <c r="J258" t="n">
-        <v>-3.864</v>
+        <v>-3.3936</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.87</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.17</v>
+        <v>-0.1517</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.76</v>
+        <v>-4.2476</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.83</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.211</v>
+        <v>-0.1916</v>
       </c>
       <c r="J260" t="n">
-        <v>-5.908</v>
+        <v>-5.3648</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.72</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3174</v>
+        <v>-0.3002</v>
       </c>
       <c r="J261" t="n">
-        <v>-8.8872</v>
+        <v>-8.4056</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.24</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3926</v>
+        <v>0.3888</v>
       </c>
       <c r="J262" t="n">
-        <v>14.1336</v>
+        <v>13.9968</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.15</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2715</v>
+        <v>0.2575</v>
       </c>
       <c r="J263" t="n">
-        <v>9.773999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.04</v>
       </c>
       <c r="I264" t="n">
-        <v>0.0978</v>
+        <v>0.083</v>
       </c>
       <c r="J264" t="n">
-        <v>3.5208</v>
+        <v>2.988</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.99</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0251</v>
+        <v>-0.0181</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.9036</v>
+        <v>-0.6516</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.57</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4631</v>
+        <v>-0.4599</v>
       </c>
       <c r="J266" t="n">
-        <v>-16.6716</v>
+        <v>-16.5564</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.36</v>
       </c>
       <c r="I267" t="n">
-        <v>0.4923</v>
+        <v>0.4241</v>
       </c>
       <c r="J267" t="n">
-        <v>17.7228</v>
+        <v>15.2676</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.32</v>
       </c>
       <c r="I268" t="n">
-        <v>0.4477</v>
+        <v>0.3816</v>
       </c>
       <c r="J268" t="n">
-        <v>16.1172</v>
+        <v>13.7376</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1.13</v>
       </c>
       <c r="I269" t="n">
-        <v>0.218</v>
+        <v>0.173</v>
       </c>
       <c r="J269" t="n">
-        <v>7.848</v>
+        <v>6.228</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.88</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1784</v>
+        <v>-0.158</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.4224</v>
+        <v>-5.688</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.84</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2211</v>
+        <v>-0.2009</v>
       </c>
       <c r="J271" t="n">
-        <v>-7.9596</v>
+        <v>-7.2324</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.34</v>
       </c>
       <c r="I272" t="n">
-        <v>0.8623</v>
+        <v>0.8408</v>
       </c>
       <c r="J272" t="n">
-        <v>30.1805</v>
+        <v>29.428</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.31</v>
       </c>
       <c r="I273" t="n">
-        <v>0.8006</v>
+        <v>0.7739</v>
       </c>
       <c r="J273" t="n">
-        <v>28.021</v>
+        <v>27.0865</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.01</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0461</v>
+        <v>0.0346</v>
       </c>
       <c r="J274" t="n">
-        <v>1.6135</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.95</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.2167</v>
+        <v>-0.1799</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.5845</v>
+        <v>-6.2965</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.83</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.535</v>
+        <v>-0.4944</v>
       </c>
       <c r="J276" t="n">
-        <v>-18.725</v>
+        <v>-17.304</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.2</v>
       </c>
       <c r="I277" t="n">
-        <v>0.4292</v>
+        <v>0.3718</v>
       </c>
       <c r="J277" t="n">
-        <v>15.022</v>
+        <v>13.013</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.13</v>
       </c>
       <c r="I278" t="n">
-        <v>0.3058</v>
+        <v>0.2551</v>
       </c>
       <c r="J278" t="n">
-        <v>10.703</v>
+        <v>8.9285</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.99</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0264</v>
+        <v>-0.0188</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.924</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.95</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.0876</v>
+        <v>-0.0716</v>
       </c>
       <c r="J280" t="n">
-        <v>-3.066</v>
+        <v>-2.506</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.83</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.224</v>
+        <v>-0.2035</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.84</v>
+        <v>-7.1225</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.2</v>
       </c>
       <c r="I282" t="n">
-        <v>0.4482</v>
+        <v>0.3911</v>
       </c>
       <c r="J282" t="n">
-        <v>12.9978</v>
+        <v>11.3419</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>1.01</v>
       </c>
       <c r="I283" t="n">
-        <v>0.0509</v>
+        <v>0.0342</v>
       </c>
       <c r="J283" t="n">
-        <v>1.4761</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.96</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.0693</v>
+        <v>-0.0565</v>
       </c>
       <c r="J284" t="n">
-        <v>-2.0097</v>
+        <v>-1.6385</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.8</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.2472</v>
+        <v>-0.2272</v>
       </c>
       <c r="J285" t="n">
-        <v>-7.1688</v>
+        <v>-6.5888</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.75</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.2957</v>
+        <v>-0.2774</v>
       </c>
       <c r="J286" t="n">
-        <v>-8.5753</v>
+        <v>-8.044600000000001</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.64</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3065</v>
+        <v>1.3288</v>
       </c>
       <c r="J287" t="n">
-        <v>37.8885</v>
+        <v>38.5352</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.36</v>
       </c>
       <c r="I288" t="n">
-        <v>0.8847</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J288" t="n">
-        <v>25.6563</v>
+        <v>25.0966</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.02</v>
       </c>
       <c r="I289" t="n">
-        <v>0.0764</v>
+        <v>0.0598</v>
       </c>
       <c r="J289" t="n">
-        <v>2.2156</v>
+        <v>1.7342</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3442</v>
+        <v>-0.3025</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.9818</v>
+        <v>-8.772500000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5702</v>
+        <v>-0.5323</v>
       </c>
       <c r="J291" t="n">
-        <v>-16.5358</v>
+        <v>-15.4367</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.17</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3711</v>
+        <v>0.3167</v>
       </c>
       <c r="J292" t="n">
-        <v>13.3596</v>
+        <v>11.4012</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.11</v>
       </c>
       <c r="I293" t="n">
-        <v>0.2631</v>
+        <v>0.2168</v>
       </c>
       <c r="J293" t="n">
-        <v>9.4716</v>
+        <v>7.8048</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.08</v>
       </c>
       <c r="I294" t="n">
-        <v>0.2048</v>
+        <v>0.1648</v>
       </c>
       <c r="J294" t="n">
-        <v>7.3728</v>
+        <v>5.9328</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>1.03</v>
       </c>
       <c r="I295" t="n">
-        <v>0.0951</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J295" t="n">
-        <v>3.4236</v>
+        <v>2.574</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.88</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.174</v>
+        <v>-0.1535</v>
       </c>
       <c r="J296" t="n">
-        <v>-6.264</v>
+        <v>-5.526</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.3</v>
       </c>
       <c r="I297" t="n">
-        <v>0.7664</v>
+        <v>0.7381</v>
       </c>
       <c r="J297" t="n">
-        <v>27.5904</v>
+        <v>26.5716</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.24</v>
       </c>
       <c r="I298" t="n">
-        <v>0.6405</v>
+        <v>0.6057</v>
       </c>
       <c r="J298" t="n">
-        <v>23.058</v>
+        <v>21.8052</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.13</v>
       </c>
       <c r="I299" t="n">
-        <v>0.3941</v>
+        <v>0.357</v>
       </c>
       <c r="J299" t="n">
-        <v>14.1876</v>
+        <v>12.852</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.13</v>
       </c>
       <c r="I300" t="n">
-        <v>0.3941</v>
+        <v>0.357</v>
       </c>
       <c r="J300" t="n">
-        <v>14.1876</v>
+        <v>12.852</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.89</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.3953</v>
+        <v>-0.353</v>
       </c>
       <c r="J301" t="n">
-        <v>-14.2308</v>
+        <v>-12.708</v>
       </c>
     </row>
   </sheetData>
